--- a/psalm/시편말씀액자_구절입력_180.xlsx
+++ b/psalm/시편말씀액자_구절입력_180.xlsx
@@ -1425,7 +1425,7 @@
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>여호와 우리 주여 주의 이름이 온 땅에 어찌 그리 아름다운지요</t>
+          <t>여호와 우리 주여 주의 이름이 온 땅에 어찌 그리 아름다운지요 주의 영광이 하늘을 덮었나이다</t>
         </is>
       </c>
       <c r="F12" s="16">
@@ -1437,7 +1437,11 @@
         <v/>
       </c>
       <c r="H12" s="16" t="n"/>
-      <c r="I12" s="17" t="n"/>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>본문 보완 2026-09-10: 절의 뒷부분 「주의 영광이 하늘을 덮었나이다」가 빠져 있었음(대한성서공회 개역개정 대조)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="n">

--- a/psalm/시편말씀액자_구절입력_180.xlsx
+++ b/psalm/시편말씀액자_구절입력_180.xlsx
@@ -1492,8 +1492,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="15" t="n"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>시편 6편 9절</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>여호와께서 내 간구를 들으셨음이여 여호와께서 내 기도를 받으시리로다</t>
+        </is>
+      </c>
       <c r="F14" s="16">
         <f>IF($E14="","",LEN(SUBSTITUTE($E14," ",""))+LEN(TRIM($E14))-LEN(SUBSTITUTE(TRIM($E14)," ",""))+1)</f>
         <v/>
@@ -1519,8 +1527,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="15" t="n"/>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>시편 8편 4절</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>사람이 무엇이기에 주께서 그를 생각하시며 인자가 무엇이기에 주께서 그를 돌보시나이까</t>
+        </is>
+      </c>
       <c r="F15" s="16">
         <f>IF($E15="","",LEN(SUBSTITUTE($E15," ",""))+LEN(TRIM($E15))-LEN(SUBSTITUTE(TRIM($E15)," ",""))+1)</f>
         <v/>
@@ -1546,8 +1562,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="15" t="n"/>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>시편 9편 9절</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>여호와는 압제를 당하는 자의 요새이시요 환난 때의 요새이시로다</t>
+        </is>
+      </c>
       <c r="F16" s="16">
         <f>IF($E16="","",LEN(SUBSTITUTE($E16," ",""))+LEN(TRIM($E16))-LEN(SUBSTITUTE(TRIM($E16)," ",""))+1)</f>
         <v/>
@@ -1573,8 +1597,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="15" t="n"/>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>시편 13편 5절</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>나는 오직 주의 사랑을 의지하였사오니 나의 마음은 주의 구원을 기뻐하리이다</t>
+        </is>
+      </c>
       <c r="F17" s="16">
         <f>IF($E17="","",LEN(SUBSTITUTE($E17," ",""))+LEN(TRIM($E17))-LEN(SUBSTITUTE(TRIM($E17)," ",""))+1)</f>
         <v/>
@@ -1600,8 +1632,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="15" t="n"/>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>시편 16편 8절</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>내가 여호와를 항상 내 앞에 모심이여 그가 나의 오른쪽에 계시므로 내가 흔들리지 아니하리로다</t>
+        </is>
+      </c>
       <c r="F18" s="16">
         <f>IF($E18="","",LEN(SUBSTITUTE($E18," ",""))+LEN(TRIM($E18))-LEN(SUBSTITUTE(TRIM($E18)," ",""))+1)</f>
         <v/>
@@ -1627,8 +1667,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="15" t="n"/>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>시편 16편 11절</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>주께서 생명의 길을 내게 보이시리니 주의 앞에는 충만한 기쁨이 있고 주의 오른쪽에는 영원한 즐거움이 있나이다</t>
+        </is>
+      </c>
       <c r="F19" s="16">
         <f>IF($E19="","",LEN(SUBSTITUTE($E19," ",""))+LEN(TRIM($E19))-LEN(SUBSTITUTE(TRIM($E19)," ",""))+1)</f>
         <v/>
@@ -1654,8 +1702,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="15" t="n"/>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>시편 18편 1절</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>나의 힘이신 여호와여 내가 주를 사랑하나이다</t>
+        </is>
+      </c>
       <c r="F20" s="16">
         <f>IF($E20="","",LEN(SUBSTITUTE($E20," ",""))+LEN(TRIM($E20))-LEN(SUBSTITUTE(TRIM($E20)," ",""))+1)</f>
         <v/>
@@ -1681,8 +1737,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="15" t="n"/>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>시편 19편 1절</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>하늘이 하나님의 영광을 선포하고 궁창이 그의 손으로 하신 일을 나타내는도다</t>
+        </is>
+      </c>
       <c r="F21" s="16">
         <f>IF($E21="","",LEN(SUBSTITUTE($E21," ",""))+LEN(TRIM($E21))-LEN(SUBSTITUTE(TRIM($E21)," ",""))+1)</f>
         <v/>
@@ -1708,8 +1772,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="15" t="n"/>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>시편 19편 14절</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>나의 반석이시요 나의 구속자이신 여호와여 내 입의 말과 마음의 묵상이 주님 앞에 열납되기를 원하나이다</t>
+        </is>
+      </c>
       <c r="F22" s="16">
         <f>IF($E22="","",LEN(SUBSTITUTE($E22," ",""))+LEN(TRIM($E22))-LEN(SUBSTITUTE(TRIM($E22)," ",""))+1)</f>
         <v/>
@@ -1735,8 +1807,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="15" t="n"/>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>시편 20편 7절</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>어떤 사람은 병거, 어떤 사람은 말을 의지하나 우리는 여호와 우리 하나님의 이름을 자랑하리로다</t>
+        </is>
+      </c>
       <c r="F23" s="16">
         <f>IF($E23="","",LEN(SUBSTITUTE($E23," ",""))+LEN(TRIM($E23))-LEN(SUBSTITUTE(TRIM($E23)," ",""))+1)</f>
         <v/>
@@ -1762,8 +1842,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="15" t="n"/>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>시편 22편 1절</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>내 하나님이여 내 하나님이여 어찌 나를 버리셨나이까 어찌 나를 멀리 하여 돕지 아니하시오며 내 신음 소리를 듣지 아니하시나이까</t>
+        </is>
+      </c>
       <c r="F24" s="16">
         <f>IF($E24="","",LEN(SUBSTITUTE($E24," ",""))+LEN(TRIM($E24))-LEN(SUBSTITUTE(TRIM($E24)," ",""))+1)</f>
         <v/>
@@ -1789,8 +1877,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="15" t="n"/>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>시편 23편 1절</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>여호와는 나의 목자시니 내게 부족함이 없으리로다</t>
+        </is>
+      </c>
       <c r="F25" s="16">
         <f>IF($E25="","",LEN(SUBSTITUTE($E25," ",""))+LEN(TRIM($E25))-LEN(SUBSTITUTE(TRIM($E25)," ",""))+1)</f>
         <v/>
@@ -1816,8 +1912,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="15" t="n"/>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>시편 23편 2절</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>그가 나를 푸른 풀밭에 누이시며 쉴 만한 물 가로 인도하시는도다</t>
+        </is>
+      </c>
       <c r="F26" s="16">
         <f>IF($E26="","",LEN(SUBSTITUTE($E26," ",""))+LEN(TRIM($E26))-LEN(SUBSTITUTE(TRIM($E26)," ",""))+1)</f>
         <v/>
@@ -1843,8 +1947,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="15" t="n"/>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>시편 23편 3절</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>내 영혼을 소생시키시고 자기 이름을 위하여 의의 길로 인도하시는도다</t>
+        </is>
+      </c>
       <c r="F27" s="16">
         <f>IF($E27="","",LEN(SUBSTITUTE($E27," ",""))+LEN(TRIM($E27))-LEN(SUBSTITUTE(TRIM($E27)," ",""))+1)</f>
         <v/>
@@ -1870,8 +1982,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D28" s="14" t="n"/>
-      <c r="E28" s="15" t="n"/>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>시편 23편 4절</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>내가 사망의 음침한 골짜기로 다닐지라도 해를 두려워하지 않을 것은 주께서 나와 함께 하심이라 주의 지팡이와 막대기가 나를 안위하시나이다</t>
+        </is>
+      </c>
       <c r="F28" s="16">
         <f>IF($E28="","",LEN(SUBSTITUTE($E28," ",""))+LEN(TRIM($E28))-LEN(SUBSTITUTE(TRIM($E28)," ",""))+1)</f>
         <v/>
@@ -1897,8 +2017,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="15" t="n"/>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>시편 23편 5절</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>주께서 내 원수의 목전에서 내게 상을 차려 주시고 기름을 내 머리에 부으셨으니 내 잔이 넘치나이다</t>
+        </is>
+      </c>
       <c r="F29" s="16">
         <f>IF($E29="","",LEN(SUBSTITUTE($E29," ",""))+LEN(TRIM($E29))-LEN(SUBSTITUTE(TRIM($E29)," ",""))+1)</f>
         <v/>
@@ -1924,8 +2052,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="15" t="n"/>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>시편 23편 6절</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>내 평생에 선하심과 인자하심이 반드시 나를 따르리니 내가 여호와의 집에 영원히 살리로다</t>
+        </is>
+      </c>
       <c r="F30" s="16">
         <f>IF($E30="","",LEN(SUBSTITUTE($E30," ",""))+LEN(TRIM($E30))-LEN(SUBSTITUTE(TRIM($E30)," ",""))+1)</f>
         <v/>
@@ -1951,8 +2087,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="15" t="n"/>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>시편 24편 1절</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>땅과 거기에 충만한 것과 세계와 그 가운데에 사는 자들은 다 여호와의 것이로다</t>
+        </is>
+      </c>
       <c r="F31" s="16">
         <f>IF($E31="","",LEN(SUBSTITUTE($E31," ",""))+LEN(TRIM($E31))-LEN(SUBSTITUTE(TRIM($E31)," ",""))+1)</f>
         <v/>
@@ -1978,8 +2122,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="15" t="n"/>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>시편 25편 4절</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>여호와여 주의 도를 내게 보이시고 주의 길을 내게 가르치소서</t>
+        </is>
+      </c>
       <c r="F32" s="16">
         <f>IF($E32="","",LEN(SUBSTITUTE($E32," ",""))+LEN(TRIM($E32))-LEN(SUBSTITUTE(TRIM($E32)," ",""))+1)</f>
         <v/>
@@ -2005,8 +2157,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="15" t="n"/>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>시편 25편 5절</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>주의 진리로 나를 지도하시고 교훈하소서 주는 내 구원의 하나님이시니 내가 종일 주를 기다리나이다</t>
+        </is>
+      </c>
       <c r="F33" s="16">
         <f>IF($E33="","",LEN(SUBSTITUTE($E33," ",""))+LEN(TRIM($E33))-LEN(SUBSTITUTE(TRIM($E33)," ",""))+1)</f>
         <v/>
@@ -2032,8 +2192,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="15" t="n"/>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>시편 27편 1절</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>여호와는 나의 빛이요 나의 구원이시니 내가 누구를 두려워하리요 여호와는 내 생명의 능력이시니 내가 누구를 무서워하리요</t>
+        </is>
+      </c>
       <c r="F34" s="16">
         <f>IF($E34="","",LEN(SUBSTITUTE($E34," ",""))+LEN(TRIM($E34))-LEN(SUBSTITUTE(TRIM($E34)," ",""))+1)</f>
         <v/>
@@ -2059,8 +2227,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="15" t="n"/>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>시편 27편 14절</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>너는 여호와를 기다릴지어다 강하고 담대하며 여호와를 기다릴지어다</t>
+        </is>
+      </c>
       <c r="F35" s="16">
         <f>IF($E35="","",LEN(SUBSTITUTE($E35," ",""))+LEN(TRIM($E35))-LEN(SUBSTITUTE(TRIM($E35)," ",""))+1)</f>
         <v/>
@@ -2086,8 +2262,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="15" t="n"/>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>시편 30편 5절</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>그의 노염은 잠깐이요 그의 은총은 평생이로다 저녁에는 울음이 깃들일지라도 아침에는 기쁨이 오리로다</t>
+        </is>
+      </c>
       <c r="F36" s="16">
         <f>IF($E36="","",LEN(SUBSTITUTE($E36," ",""))+LEN(TRIM($E36))-LEN(SUBSTITUTE(TRIM($E36)," ",""))+1)</f>
         <v/>
@@ -2113,8 +2297,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="15" t="n"/>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>시편 31편 3절</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>주는 나의 반석과 산성이시니 그러므로 주의 이름을 생각하셔서 나를 인도하시고 지도하소서</t>
+        </is>
+      </c>
       <c r="F37" s="16">
         <f>IF($E37="","",LEN(SUBSTITUTE($E37," ",""))+LEN(TRIM($E37))-LEN(SUBSTITUTE(TRIM($E37)," ",""))+1)</f>
         <v/>
@@ -2140,8 +2332,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="15" t="n"/>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>시편 32편 8절</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>내가 네 갈 길을 가르쳐 보이고 너를 주목하여 훈계하리로다</t>
+        </is>
+      </c>
       <c r="F38" s="16">
         <f>IF($E38="","",LEN(SUBSTITUTE($E38," ",""))+LEN(TRIM($E38))-LEN(SUBSTITUTE(TRIM($E38)," ",""))+1)</f>
         <v/>
@@ -2167,8 +2367,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D39" s="14" t="n"/>
-      <c r="E39" s="15" t="n"/>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>시편 33편 12절</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>여호와를 자기 하나님으로 삼은 나라 곧 하나님의 기업으로 선택된 백성은 복이 있도다</t>
+        </is>
+      </c>
       <c r="F39" s="16">
         <f>IF($E39="","",LEN(SUBSTITUTE($E39," ",""))+LEN(TRIM($E39))-LEN(SUBSTITUTE(TRIM($E39)," ",""))+1)</f>
         <v/>
@@ -2194,8 +2402,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D40" s="14" t="n"/>
-      <c r="E40" s="15" t="n"/>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>시편 34편 1절</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>내가 여호와를 항상 송축함이여 내 입술로 항상 주를 찬양하리이다</t>
+        </is>
+      </c>
       <c r="F40" s="16">
         <f>IF($E40="","",LEN(SUBSTITUTE($E40," ",""))+LEN(TRIM($E40))-LEN(SUBSTITUTE(TRIM($E40)," ",""))+1)</f>
         <v/>
@@ -2221,8 +2437,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D41" s="14" t="n"/>
-      <c r="E41" s="15" t="n"/>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>시편 34편 8절</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>너희는 여호와의 선하심을 맛보아 알지어다 그에게 피하는 자는 복이 있도다</t>
+        </is>
+      </c>
       <c r="F41" s="16">
         <f>IF($E41="","",LEN(SUBSTITUTE($E41," ",""))+LEN(TRIM($E41))-LEN(SUBSTITUTE(TRIM($E41)," ",""))+1)</f>
         <v/>
@@ -2248,8 +2472,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="15" t="n"/>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>시편 34편 18절</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>여호와는 마음이 상한 자를 가까이 하시고 충심으로 통회하는 자를 구원하시는도다</t>
+        </is>
+      </c>
       <c r="F42" s="16">
         <f>IF($E42="","",LEN(SUBSTITUTE($E42," ",""))+LEN(TRIM($E42))-LEN(SUBSTITUTE(TRIM($E42)," ",""))+1)</f>
         <v/>
@@ -2275,8 +2507,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D43" s="14" t="n"/>
-      <c r="E43" s="15" t="n"/>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>시편 34편 19절</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>의인은 고난이 많으나 여호와께서 그의 모든 고난에서 건지시는도다</t>
+        </is>
+      </c>
       <c r="F43" s="16">
         <f>IF($E43="","",LEN(SUBSTITUTE($E43," ",""))+LEN(TRIM($E43))-LEN(SUBSTITUTE(TRIM($E43)," ",""))+1)</f>
         <v/>
@@ -2302,8 +2542,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D44" s="14" t="n"/>
-      <c r="E44" s="15" t="n"/>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>시편 37편 3절</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>여호와를 의뢰하고 선을 행하라 땅에 머무는 동안 그의 성실을 먹을 거리로 삼을지어다</t>
+        </is>
+      </c>
       <c r="F44" s="16">
         <f>IF($E44="","",LEN(SUBSTITUTE($E44," ",""))+LEN(TRIM($E44))-LEN(SUBSTITUTE(TRIM($E44)," ",""))+1)</f>
         <v/>
@@ -2329,8 +2577,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D45" s="14" t="n"/>
-      <c r="E45" s="15" t="n"/>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>시편 37편 4절</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>또 여호와를 기뻐하라 그가 네 마음의 소원을 네게 이루어 주시리로다</t>
+        </is>
+      </c>
       <c r="F45" s="16">
         <f>IF($E45="","",LEN(SUBSTITUTE($E45," ",""))+LEN(TRIM($E45))-LEN(SUBSTITUTE(TRIM($E45)," ",""))+1)</f>
         <v/>
@@ -2356,8 +2612,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="15" t="n"/>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>시편 37편 5절</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>네 길을 여호와께 맡기라 그를 의지하면 그가 이루시고</t>
+        </is>
+      </c>
       <c r="F46" s="16">
         <f>IF($E46="","",LEN(SUBSTITUTE($E46," ",""))+LEN(TRIM($E46))-LEN(SUBSTITUTE(TRIM($E46)," ",""))+1)</f>
         <v/>
@@ -2383,8 +2647,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D47" s="14" t="n"/>
-      <c r="E47" s="15" t="n"/>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>시편 40편 1절</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>내가 여호와를 기다리고 기다렸더니 귀를 기울이사 나의 부르짖음을 들으셨도다</t>
+        </is>
+      </c>
       <c r="F47" s="16">
         <f>IF($E47="","",LEN(SUBSTITUTE($E47," ",""))+LEN(TRIM($E47))-LEN(SUBSTITUTE(TRIM($E47)," ",""))+1)</f>
         <v/>
@@ -2410,8 +2682,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D48" s="14" t="n"/>
-      <c r="E48" s="15" t="n"/>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>시편 42편 1절</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>하나님이여 사슴이 시냇물을 찾기에 갈급함 같이 내 영혼이 주를 찾기에 갈급하니이다</t>
+        </is>
+      </c>
       <c r="F48" s="16">
         <f>IF($E48="","",LEN(SUBSTITUTE($E48," ",""))+LEN(TRIM($E48))-LEN(SUBSTITUTE(TRIM($E48)," ",""))+1)</f>
         <v/>
@@ -2437,8 +2717,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D49" s="14" t="n"/>
-      <c r="E49" s="15" t="n"/>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>시편 46편 1절</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>하나님은 우리의 피난처시요 힘이시니 환난 중에 만날 큰 도움이시라</t>
+        </is>
+      </c>
       <c r="F49" s="16">
         <f>IF($E49="","",LEN(SUBSTITUTE($E49," ",""))+LEN(TRIM($E49))-LEN(SUBSTITUTE(TRIM($E49)," ",""))+1)</f>
         <v/>
@@ -2464,8 +2752,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D50" s="14" t="n"/>
-      <c r="E50" s="15" t="n"/>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>시편 51편 10절</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>하나님이여 내 속에 정한 마음을 창조하시고 내 안에 정직한 영을 새롭게 하소서</t>
+        </is>
+      </c>
       <c r="F50" s="16">
         <f>IF($E50="","",LEN(SUBSTITUTE($E50," ",""))+LEN(TRIM($E50))-LEN(SUBSTITUTE(TRIM($E50)," ",""))+1)</f>
         <v/>
@@ -2491,8 +2787,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D51" s="14" t="n"/>
-      <c r="E51" s="15" t="n"/>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>시편 51편 17절</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>하나님께서 구하시는 제사는 상한 심령이라 하나님이여 상하고 통회하는 마음을 주께서 멸시하지 아니하시리이다</t>
+        </is>
+      </c>
       <c r="F51" s="16">
         <f>IF($E51="","",LEN(SUBSTITUTE($E51," ",""))+LEN(TRIM($E51))-LEN(SUBSTITUTE(TRIM($E51)," ",""))+1)</f>
         <v/>
@@ -2518,8 +2822,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="15" t="n"/>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>시편 55편 22절</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>네 짐을 여호와께 맡기라 그가 너를 붙드시고 의인의 요동함을 영원히 허락하지 아니하시리로다</t>
+        </is>
+      </c>
       <c r="F52" s="16">
         <f>IF($E52="","",LEN(SUBSTITUTE($E52," ",""))+LEN(TRIM($E52))-LEN(SUBSTITUTE(TRIM($E52)," ",""))+1)</f>
         <v/>
@@ -2545,8 +2857,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D53" s="14" t="n"/>
-      <c r="E53" s="15" t="n"/>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>시편 56편 3절</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>내가 두려워하는 날에는 내가 주를 의지하리이다</t>
+        </is>
+      </c>
       <c r="F53" s="16">
         <f>IF($E53="","",LEN(SUBSTITUTE($E53," ",""))+LEN(TRIM($E53))-LEN(SUBSTITUTE(TRIM($E53)," ",""))+1)</f>
         <v/>
@@ -2572,8 +2892,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D54" s="14" t="n"/>
-      <c r="E54" s="15" t="n"/>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>시편 61편 2절</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>내 마음이 약해 질 때에 땅 끝에서부터 주께 부르짖으오리니 나보다 높은 바위에 나를 인도하소서</t>
+        </is>
+      </c>
       <c r="F54" s="16">
         <f>IF($E54="","",LEN(SUBSTITUTE($E54," ",""))+LEN(TRIM($E54))-LEN(SUBSTITUTE(TRIM($E54)," ",""))+1)</f>
         <v/>
@@ -2599,8 +2927,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D55" s="14" t="n"/>
-      <c r="E55" s="15" t="n"/>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>시편 62편 1절</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>나의 영혼이 잠잠히 하나님만 바람이여 나의 구원이 그에게서 나오는도다</t>
+        </is>
+      </c>
       <c r="F55" s="16">
         <f>IF($E55="","",LEN(SUBSTITUTE($E55," ",""))+LEN(TRIM($E55))-LEN(SUBSTITUTE(TRIM($E55)," ",""))+1)</f>
         <v/>
@@ -2626,8 +2962,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D56" s="14" t="n"/>
-      <c r="E56" s="15" t="n"/>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>시편 66편 18절</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>내가 나의 마음에 죄악을 품었더라면 주께서 듣지 아니하시리라</t>
+        </is>
+      </c>
       <c r="F56" s="16">
         <f>IF($E56="","",LEN(SUBSTITUTE($E56," ",""))+LEN(TRIM($E56))-LEN(SUBSTITUTE(TRIM($E56)," ",""))+1)</f>
         <v/>
@@ -2653,8 +2997,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D57" s="14" t="n"/>
-      <c r="E57" s="15" t="n"/>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>시편 73편 26절</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>내 육체와 마음은 쇠약하나 하나님은 내 마음의 반석이시요 영원한 분깃이시라</t>
+        </is>
+      </c>
       <c r="F57" s="16">
         <f>IF($E57="","",LEN(SUBSTITUTE($E57," ",""))+LEN(TRIM($E57))-LEN(SUBSTITUTE(TRIM($E57)," ",""))+1)</f>
         <v/>
@@ -2680,8 +3032,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D58" s="14" t="n"/>
-      <c r="E58" s="15" t="n"/>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>시편 84편 10절</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>주의 궁정에서의 한 날이 다른 곳에서의 천 날보다 나은즉 악인의 장막에 사는 것보다 내 하나님의 성전 문지기로 있는 것이 좋사오니</t>
+        </is>
+      </c>
       <c r="F58" s="16">
         <f>IF($E58="","",LEN(SUBSTITUTE($E58," ",""))+LEN(TRIM($E58))-LEN(SUBSTITUTE(TRIM($E58)," ",""))+1)</f>
         <v/>
@@ -2707,8 +3067,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D59" s="14" t="n"/>
-      <c r="E59" s="15" t="n"/>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>시편 84편 11절</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>여호와 하나님은 해요 방패이시라 여호와께서 은혜와 영화를 주시며 정직하게 행하는 자에게 좋은 것을 아끼지 아니하실 것임이니이다</t>
+        </is>
+      </c>
       <c r="F59" s="16">
         <f>IF($E59="","",LEN(SUBSTITUTE($E59," ",""))+LEN(TRIM($E59))-LEN(SUBSTITUTE(TRIM($E59)," ",""))+1)</f>
         <v/>
@@ -2734,8 +3102,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D60" s="14" t="n"/>
-      <c r="E60" s="15" t="n"/>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>시편 86편 5절</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>주는 선하사 사죄하기를 즐거워하시며 주께 부르짖는 자에게 인자함이 후하심이니이다</t>
+        </is>
+      </c>
       <c r="F60" s="16">
         <f>IF($E60="","",LEN(SUBSTITUTE($E60," ",""))+LEN(TRIM($E60))-LEN(SUBSTITUTE(TRIM($E60)," ",""))+1)</f>
         <v/>
@@ -2761,8 +3137,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D61" s="14" t="n"/>
-      <c r="E61" s="15" t="n"/>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>시편 86편 11절</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>여호와여 주의 도를 내게 가르치소서 내가 주의 진리에 행하오리니 일심으로 주의 이름을 경외하게 하소서</t>
+        </is>
+      </c>
       <c r="F61" s="16">
         <f>IF($E61="","",LEN(SUBSTITUTE($E61," ",""))+LEN(TRIM($E61))-LEN(SUBSTITUTE(TRIM($E61)," ",""))+1)</f>
         <v/>
@@ -2788,8 +3172,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D62" s="14" t="n"/>
-      <c r="E62" s="15" t="n"/>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>시편 90편 12절</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>우리에게 우리 날 계수함을 가르치사 지혜로운 마음을 얻게 하소서</t>
+        </is>
+      </c>
       <c r="F62" s="16">
         <f>IF($E62="","",LEN(SUBSTITUTE($E62," ",""))+LEN(TRIM($E62))-LEN(SUBSTITUTE(TRIM($E62)," ",""))+1)</f>
         <v/>
@@ -2815,8 +3207,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D63" s="14" t="n"/>
-      <c r="E63" s="15" t="n"/>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>시편 91편 1절</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>지존자의 은밀한 곳에 거주하며 전능자의 그늘 아래에 사는 자여,</t>
+        </is>
+      </c>
       <c r="F63" s="16">
         <f>IF($E63="","",LEN(SUBSTITUTE($E63," ",""))+LEN(TRIM($E63))-LEN(SUBSTITUTE(TRIM($E63)," ",""))+1)</f>
         <v/>
@@ -2842,8 +3242,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D64" s="14" t="n"/>
-      <c r="E64" s="15" t="n"/>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>시편 91편 2절</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>나는 여호와를 향하여 말하기를 그는 나의 피난처요 나의 요새요 내가 의뢰하는 하나님이라 하리니</t>
+        </is>
+      </c>
       <c r="F64" s="16">
         <f>IF($E64="","",LEN(SUBSTITUTE($E64," ",""))+LEN(TRIM($E64))-LEN(SUBSTITUTE(TRIM($E64)," ",""))+1)</f>
         <v/>
@@ -2869,8 +3277,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D65" s="14" t="n"/>
-      <c r="E65" s="15" t="n"/>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>시편 91편 11절</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>그가 너를 위하여 그의 천사들을 명령하사 네 모든 길에서 너를 지키게 하심이라</t>
+        </is>
+      </c>
       <c r="F65" s="16">
         <f>IF($E65="","",LEN(SUBSTITUTE($E65," ",""))+LEN(TRIM($E65))-LEN(SUBSTITUTE(TRIM($E65)," ",""))+1)</f>
         <v/>
@@ -2896,8 +3312,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D66" s="14" t="n"/>
-      <c r="E66" s="15" t="n"/>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>시편 95편 1절</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>오라 우리가 여호와께 노래하며 우리의 구원의 반석을 향하여 즐거이 외치자</t>
+        </is>
+      </c>
       <c r="F66" s="16">
         <f>IF($E66="","",LEN(SUBSTITUTE($E66," ",""))+LEN(TRIM($E66))-LEN(SUBSTITUTE(TRIM($E66)," ",""))+1)</f>
         <v/>
@@ -2923,8 +3347,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D67" s="14" t="n"/>
-      <c r="E67" s="15" t="n"/>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>시편 95편 6절</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>오라 우리가 굽혀 경배하며 우리를 지으신 여호와 앞에 무릎을 꿇자</t>
+        </is>
+      </c>
       <c r="F67" s="16">
         <f>IF($E67="","",LEN(SUBSTITUTE($E67," ",""))+LEN(TRIM($E67))-LEN(SUBSTITUTE(TRIM($E67)," ",""))+1)</f>
         <v/>
@@ -2950,8 +3382,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D68" s="14" t="n"/>
-      <c r="E68" s="15" t="n"/>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>시편 96편 1절</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>새 노래로 여호와께 노래하라 온 땅이여 여호와께 노래할지어다</t>
+        </is>
+      </c>
       <c r="F68" s="16">
         <f>IF($E68="","",LEN(SUBSTITUTE($E68," ",""))+LEN(TRIM($E68))-LEN(SUBSTITUTE(TRIM($E68)," ",""))+1)</f>
         <v/>
@@ -2977,8 +3417,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D69" s="14" t="n"/>
-      <c r="E69" s="15" t="n"/>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>시편 100편 1-2절</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>온 땅이여 여호와께 즐거운 찬송을 부를지어다 기쁨으로 여호와를 섬기며 노래하면서 그의 앞에 나아갈지어다</t>
+        </is>
+      </c>
       <c r="F69" s="16">
         <f>IF($E69="","",LEN(SUBSTITUTE($E69," ",""))+LEN(TRIM($E69))-LEN(SUBSTITUTE(TRIM($E69)," ",""))+1)</f>
         <v/>
@@ -3004,8 +3452,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D70" s="14" t="n"/>
-      <c r="E70" s="15" t="n"/>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>시편 100편 5절</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>여호와는 선하시니 그의 인자하심이 영원하고 그의 성실하심이 대대에 이르리로다</t>
+        </is>
+      </c>
       <c r="F70" s="16">
         <f>IF($E70="","",LEN(SUBSTITUTE($E70," ",""))+LEN(TRIM($E70))-LEN(SUBSTITUTE(TRIM($E70)," ",""))+1)</f>
         <v/>
@@ -3031,8 +3487,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D71" s="14" t="n"/>
-      <c r="E71" s="15" t="n"/>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>시편 103편 1절</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>내 영혼아 여호와를 송축하라 내 속에 있는 것들아 다 그의 거룩한 이름을 송축하라</t>
+        </is>
+      </c>
       <c r="F71" s="16">
         <f>IF($E71="","",LEN(SUBSTITUTE($E71," ",""))+LEN(TRIM($E71))-LEN(SUBSTITUTE(TRIM($E71)," ",""))+1)</f>
         <v/>
@@ -3058,8 +3522,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D72" s="14" t="n"/>
-      <c r="E72" s="15" t="n"/>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>시편 103편 2절</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>내 영혼아 여호와를 송축하며 그의 모든 은택을 잊지 말지어다</t>
+        </is>
+      </c>
       <c r="F72" s="16">
         <f>IF($E72="","",LEN(SUBSTITUTE($E72," ",""))+LEN(TRIM($E72))-LEN(SUBSTITUTE(TRIM($E72)," ",""))+1)</f>
         <v/>
@@ -3085,8 +3557,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D73" s="14" t="n"/>
-      <c r="E73" s="15" t="n"/>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>시편 103편 12절</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>동이 서에서 먼 것 같이 우리의 죄과를 우리에게서 멀리 옮기셨으며</t>
+        </is>
+      </c>
       <c r="F73" s="16">
         <f>IF($E73="","",LEN(SUBSTITUTE($E73," ",""))+LEN(TRIM($E73))-LEN(SUBSTITUTE(TRIM($E73)," ",""))+1)</f>
         <v/>
@@ -3112,8 +3592,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D74" s="14" t="n"/>
-      <c r="E74" s="15" t="n"/>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>시편 105편 4절</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>여호와와 그의 능력을 구할지어다 그의 얼굴을 항상 구할지어다</t>
+        </is>
+      </c>
       <c r="F74" s="16">
         <f>IF($E74="","",LEN(SUBSTITUTE($E74," ",""))+LEN(TRIM($E74))-LEN(SUBSTITUTE(TRIM($E74)," ",""))+1)</f>
         <v/>
@@ -3139,8 +3627,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D75" s="14" t="n"/>
-      <c r="E75" s="15" t="n"/>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>시편 107편 1절</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>여호와께 감사하라 그는 선하시며 그 인자하심이 영원함이로다</t>
+        </is>
+      </c>
       <c r="F75" s="16">
         <f>IF($E75="","",LEN(SUBSTITUTE($E75," ",""))+LEN(TRIM($E75))-LEN(SUBSTITUTE(TRIM($E75)," ",""))+1)</f>
         <v/>
@@ -3166,8 +3662,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D76" s="14" t="n"/>
-      <c r="E76" s="15" t="n"/>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>시편 112편 1절</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>할렐루야, 여호와를 경외하며 그의 계명을 크게 즐거워하는 자는 복이 있도다</t>
+        </is>
+      </c>
       <c r="F76" s="16">
         <f>IF($E76="","",LEN(SUBSTITUTE($E76," ",""))+LEN(TRIM($E76))-LEN(SUBSTITUTE(TRIM($E76)," ",""))+1)</f>
         <v/>
@@ -3193,8 +3697,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D77" s="14" t="n"/>
-      <c r="E77" s="15" t="n"/>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>시편 116편 12절</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>내게 주신 모든 은혜를 내가 여호와께 무엇으로 보답할까</t>
+        </is>
+      </c>
       <c r="F77" s="16">
         <f>IF($E77="","",LEN(SUBSTITUTE($E77," ",""))+LEN(TRIM($E77))-LEN(SUBSTITUTE(TRIM($E77)," ",""))+1)</f>
         <v/>
@@ -3220,8 +3732,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D78" s="14" t="n"/>
-      <c r="E78" s="15" t="n"/>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>시편 118편 8절</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>여호와께 피하는 것이 사람을 신뢰하는 것보다 나으며</t>
+        </is>
+      </c>
       <c r="F78" s="16">
         <f>IF($E78="","",LEN(SUBSTITUTE($E78," ",""))+LEN(TRIM($E78))-LEN(SUBSTITUTE(TRIM($E78)," ",""))+1)</f>
         <v/>
@@ -3247,8 +3767,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D79" s="14" t="n"/>
-      <c r="E79" s="15" t="n"/>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>시편 118편 24절</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>이 날은 여호와께서 정하신 것이라 이 날에 우리가 즐거워하고 기뻐하리로다</t>
+        </is>
+      </c>
       <c r="F79" s="16">
         <f>IF($E79="","",LEN(SUBSTITUTE($E79," ",""))+LEN(TRIM($E79))-LEN(SUBSTITUTE(TRIM($E79)," ",""))+1)</f>
         <v/>
@@ -3274,8 +3802,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D80" s="14" t="n"/>
-      <c r="E80" s="15" t="n"/>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>시편 119편 9절</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>청년이 무엇으로 그의 행실을 깨끗하게 하리이까 주의 말씀만 지킬 따름이니이다</t>
+        </is>
+      </c>
       <c r="F80" s="16">
         <f>IF($E80="","",LEN(SUBSTITUTE($E80," ",""))+LEN(TRIM($E80))-LEN(SUBSTITUTE(TRIM($E80)," ",""))+1)</f>
         <v/>
@@ -3301,8 +3837,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D81" s="14" t="n"/>
-      <c r="E81" s="15" t="n"/>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>시편 119편 11절</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>내가 주께 범죄하지 아니하려 하여 주의 말씀을 내 마음에 두었나이다</t>
+        </is>
+      </c>
       <c r="F81" s="16">
         <f>IF($E81="","",LEN(SUBSTITUTE($E81," ",""))+LEN(TRIM($E81))-LEN(SUBSTITUTE(TRIM($E81)," ",""))+1)</f>
         <v/>
@@ -3328,8 +3872,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D82" s="14" t="n"/>
-      <c r="E82" s="15" t="n"/>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>시편 119편 50절</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>이 말씀은 나의 고난 중의 위로라 주의 말씀이 나를 살리셨기 때문이니이다</t>
+        </is>
+      </c>
       <c r="F82" s="16">
         <f>IF($E82="","",LEN(SUBSTITUTE($E82," ",""))+LEN(TRIM($E82))-LEN(SUBSTITUTE(TRIM($E82)," ",""))+1)</f>
         <v/>
@@ -3355,8 +3907,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D83" s="14" t="n"/>
-      <c r="E83" s="15" t="n"/>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>시편 119편 105절</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>주의 말씀은 내 발에 등이요 내 길에 빛이니이다</t>
+        </is>
+      </c>
       <c r="F83" s="16">
         <f>IF($E83="","",LEN(SUBSTITUTE($E83," ",""))+LEN(TRIM($E83))-LEN(SUBSTITUTE(TRIM($E83)," ",""))+1)</f>
         <v/>
@@ -3382,8 +3942,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D84" s="14" t="n"/>
-      <c r="E84" s="15" t="n"/>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>시편 119편 130절</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>주의 말씀을 열면 빛이 비치어 우둔한 사람들을 깨닫게 하나이다</t>
+        </is>
+      </c>
       <c r="F84" s="16">
         <f>IF($E84="","",LEN(SUBSTITUTE($E84," ",""))+LEN(TRIM($E84))-LEN(SUBSTITUTE(TRIM($E84)," ",""))+1)</f>
         <v/>
@@ -3409,8 +3977,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D85" s="14" t="n"/>
-      <c r="E85" s="15" t="n"/>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>시편 119편 165절</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>주의 법을 사랑하는 자에게는 큰 평안이 있으니 그들에게 장애물이 없으리이다</t>
+        </is>
+      </c>
       <c r="F85" s="16">
         <f>IF($E85="","",LEN(SUBSTITUTE($E85," ",""))+LEN(TRIM($E85))-LEN(SUBSTITUTE(TRIM($E85)," ",""))+1)</f>
         <v/>
@@ -3436,8 +4012,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D86" s="14" t="n"/>
-      <c r="E86" s="15" t="n"/>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>시편 121편 1-2절</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>내가 산을 향하여 눈을 들리라 나의 도움이 어디서 올까 나의 도움은 천지를 지으신 여호와에게서로다</t>
+        </is>
+      </c>
       <c r="F86" s="16">
         <f>IF($E86="","",LEN(SUBSTITUTE($E86," ",""))+LEN(TRIM($E86))-LEN(SUBSTITUTE(TRIM($E86)," ",""))+1)</f>
         <v/>
@@ -3463,8 +4047,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D87" s="14" t="n"/>
-      <c r="E87" s="15" t="n"/>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>시편 121편 7절</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>여호와께서 너를 지켜 모든 환난을 면하게 하시며 또 네 영혼을 지키시리로다</t>
+        </is>
+      </c>
       <c r="F87" s="16">
         <f>IF($E87="","",LEN(SUBSTITUTE($E87," ",""))+LEN(TRIM($E87))-LEN(SUBSTITUTE(TRIM($E87)," ",""))+1)</f>
         <v/>
@@ -3490,8 +4082,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D88" s="14" t="n"/>
-      <c r="E88" s="15" t="n"/>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>시편 121편 8절</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>여호와께서 너의 출입을 지금부터 영원까지 지키시리로다</t>
+        </is>
+      </c>
       <c r="F88" s="16">
         <f>IF($E88="","",LEN(SUBSTITUTE($E88," ",""))+LEN(TRIM($E88))-LEN(SUBSTITUTE(TRIM($E88)," ",""))+1)</f>
         <v/>
@@ -3517,8 +4117,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D89" s="14" t="n"/>
-      <c r="E89" s="15" t="n"/>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>시편 122편 1절</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>사람이 내게 말하기를 여호와의 집에 올라가자 할 때에 내가 기뻐하였도다</t>
+        </is>
+      </c>
       <c r="F89" s="16">
         <f>IF($E89="","",LEN(SUBSTITUTE($E89," ",""))+LEN(TRIM($E89))-LEN(SUBSTITUTE(TRIM($E89)," ",""))+1)</f>
         <v/>
@@ -3544,8 +4152,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D90" s="14" t="n"/>
-      <c r="E90" s="15" t="n"/>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>시편 126편 5절</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>눈물을 흘리며 씨를 뿌리는 자는 기쁨으로 거두리로다</t>
+        </is>
+      </c>
       <c r="F90" s="16">
         <f>IF($E90="","",LEN(SUBSTITUTE($E90," ",""))+LEN(TRIM($E90))-LEN(SUBSTITUTE(TRIM($E90)," ",""))+1)</f>
         <v/>
@@ -3571,8 +4187,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D91" s="14" t="n"/>
-      <c r="E91" s="15" t="n"/>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>시편 126편 6절</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>울며 씨를 뿌리러 나가는 자는 반드시 기쁨으로 그 곡식 단을 가지고 돌아오리로다</t>
+        </is>
+      </c>
       <c r="F91" s="16">
         <f>IF($E91="","",LEN(SUBSTITUTE($E91," ",""))+LEN(TRIM($E91))-LEN(SUBSTITUTE(TRIM($E91)," ",""))+1)</f>
         <v/>
@@ -3598,8 +4222,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D92" s="14" t="n"/>
-      <c r="E92" s="15" t="n"/>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>시편 127편 1절</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>여호와께서 집을 세우지 아니하시면 세우는 자의 수고가 헛되며 여호와께서 성을 지키지 아니하시면 파수꾼의 깨어 있음이 헛되도다</t>
+        </is>
+      </c>
       <c r="F92" s="16">
         <f>IF($E92="","",LEN(SUBSTITUTE($E92," ",""))+LEN(TRIM($E92))-LEN(SUBSTITUTE(TRIM($E92)," ",""))+1)</f>
         <v/>
@@ -3625,8 +4257,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D93" s="14" t="n"/>
-      <c r="E93" s="15" t="n"/>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>시편 130편 5절</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>나 곧 내 영혼은 여호와를 기다리며 나는 주의 말씀을 바라는도다</t>
+        </is>
+      </c>
       <c r="F93" s="16">
         <f>IF($E93="","",LEN(SUBSTITUTE($E93," ",""))+LEN(TRIM($E93))-LEN(SUBSTITUTE(TRIM($E93)," ",""))+1)</f>
         <v/>
@@ -3652,8 +4292,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D94" s="14" t="n"/>
-      <c r="E94" s="15" t="n"/>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>시편 133편 1절</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>보라 형제가 연합하여 동거함이 어찌 그리 선하고 아름다운고</t>
+        </is>
+      </c>
       <c r="F94" s="16">
         <f>IF($E94="","",LEN(SUBSTITUTE($E94," ",""))+LEN(TRIM($E94))-LEN(SUBSTITUTE(TRIM($E94)," ",""))+1)</f>
         <v/>
@@ -3679,8 +4327,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D95" s="14" t="n"/>
-      <c r="E95" s="15" t="n"/>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>시편 139편 1절</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>여호와여 주께서 나를 살펴 보셨으므로 나를 아시나이다</t>
+        </is>
+      </c>
       <c r="F95" s="16">
         <f>IF($E95="","",LEN(SUBSTITUTE($E95," ",""))+LEN(TRIM($E95))-LEN(SUBSTITUTE(TRIM($E95)," ",""))+1)</f>
         <v/>
@@ -3706,8 +4362,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D96" s="14" t="n"/>
-      <c r="E96" s="15" t="n"/>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>시편 139편 14절</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>내가 주께 감사하옴은 나를 지으심이 심히 기묘하심이라 주께서 하시는 일이 기이함을 내 영혼이 잘 아나이다</t>
+        </is>
+      </c>
       <c r="F96" s="16">
         <f>IF($E96="","",LEN(SUBSTITUTE($E96," ",""))+LEN(TRIM($E96))-LEN(SUBSTITUTE(TRIM($E96)," ",""))+1)</f>
         <v/>
@@ -3733,8 +4397,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D97" s="14" t="n"/>
-      <c r="E97" s="15" t="n"/>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>시편 139편 23절</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>하나님이여 나를 살피사 내 마음을 아시며 나를 시험하사 내 뜻을 아옵소서</t>
+        </is>
+      </c>
       <c r="F97" s="16">
         <f>IF($E97="","",LEN(SUBSTITUTE($E97," ",""))+LEN(TRIM($E97))-LEN(SUBSTITUTE(TRIM($E97)," ",""))+1)</f>
         <v/>
@@ -3760,8 +4432,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D98" s="14" t="n"/>
-      <c r="E98" s="15" t="n"/>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>시편 139편 24절</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>내게 무슨 악한 행위가 있나 보시고 나를 영원한 길로 인도하소서</t>
+        </is>
+      </c>
       <c r="F98" s="16">
         <f>IF($E98="","",LEN(SUBSTITUTE($E98," ",""))+LEN(TRIM($E98))-LEN(SUBSTITUTE(TRIM($E98)," ",""))+1)</f>
         <v/>
@@ -3787,8 +4467,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D99" s="14" t="n"/>
-      <c r="E99" s="15" t="n"/>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>시편 145편 8절</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>여호와는 은혜로우시며 긍휼이 많으시며 노하기를 더디 하시며 인자하심이 크시도다</t>
+        </is>
+      </c>
       <c r="F99" s="16">
         <f>IF($E99="","",LEN(SUBSTITUTE($E99," ",""))+LEN(TRIM($E99))-LEN(SUBSTITUTE(TRIM($E99)," ",""))+1)</f>
         <v/>
@@ -3814,8 +4502,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D100" s="14" t="n"/>
-      <c r="E100" s="15" t="n"/>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>시편 145편 9절</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>여호와께서는 모든 것을 선대하시며 그 지으신 모든 것에 긍휼을 베푸시는도다</t>
+        </is>
+      </c>
       <c r="F100" s="16">
         <f>IF($E100="","",LEN(SUBSTITUTE($E100," ",""))+LEN(TRIM($E100))-LEN(SUBSTITUTE(TRIM($E100)," ",""))+1)</f>
         <v/>
@@ -3841,8 +4537,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D101" s="14" t="n"/>
-      <c r="E101" s="15" t="n"/>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>시편 145편 18절</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>여호와께서는 자기에게 간구하는 모든 자 곧 진실하게 간구하는 모든 자에게 가까이 하시는도다</t>
+        </is>
+      </c>
       <c r="F101" s="16">
         <f>IF($E101="","",LEN(SUBSTITUTE($E101," ",""))+LEN(TRIM($E101))-LEN(SUBSTITUTE(TRIM($E101)," ",""))+1)</f>
         <v/>
@@ -3868,8 +4572,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D102" s="14" t="n"/>
-      <c r="E102" s="15" t="n"/>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>시편 146편 2절</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>나의 생전에 여호와를 찬양하며 나의 평생에 내 하나님을 찬송하리로다</t>
+        </is>
+      </c>
       <c r="F102" s="16">
         <f>IF($E102="","",LEN(SUBSTITUTE($E102," ",""))+LEN(TRIM($E102))-LEN(SUBSTITUTE(TRIM($E102)," ",""))+1)</f>
         <v/>
@@ -3895,8 +4607,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D103" s="14" t="n"/>
-      <c r="E103" s="15" t="n"/>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>시편 147편 3절</t>
+        </is>
+      </c>
+      <c r="E103" s="15" t="inlineStr">
+        <is>
+          <t>상심한 자들을 고치시며 그들의 상처를 싸매시는도다</t>
+        </is>
+      </c>
       <c r="F103" s="16">
         <f>IF($E103="","",LEN(SUBSTITUTE($E103," ",""))+LEN(TRIM($E103))-LEN(SUBSTITUTE(TRIM($E103)," ",""))+1)</f>
         <v/>
@@ -3922,8 +4642,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D104" s="14" t="n"/>
-      <c r="E104" s="15" t="n"/>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>시편 150편 6절</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>호흡이 있는 자마다 여호와를 찬양할지어다 할렐루야</t>
+        </is>
+      </c>
       <c r="F104" s="16">
         <f>IF($E104="","",LEN(SUBSTITUTE($E104," ",""))+LEN(TRIM($E104))-LEN(SUBSTITUTE(TRIM($E104)," ",""))+1)</f>
         <v/>

--- a/psalm/시편말씀액자_구절입력_180.xlsx
+++ b/psalm/시편말씀액자_구절입력_180.xlsx
@@ -4677,8 +4677,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D105" s="14" t="n"/>
-      <c r="E105" s="15" t="n"/>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>잠언 1장 7절</t>
+        </is>
+      </c>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>여호와를 경외하는 것이 지식의 근본이거늘 미련한 자는 지혜와 훈계를 멸시하느니라</t>
+        </is>
+      </c>
       <c r="F105" s="16">
         <f>IF($E105="","",LEN(SUBSTITUTE($E105," ",""))+LEN(TRIM($E105))-LEN(SUBSTITUTE(TRIM($E105)," ",""))+1)</f>
         <v/>
@@ -4704,8 +4712,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D106" s="14" t="n"/>
-      <c r="E106" s="15" t="n"/>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>잠언 1장 8절</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>내 아들아 네 아비의 훈계를 들으며 네 어미의 법을 떠나지 말라</t>
+        </is>
+      </c>
       <c r="F106" s="16">
         <f>IF($E106="","",LEN(SUBSTITUTE($E106," ",""))+LEN(TRIM($E106))-LEN(SUBSTITUTE(TRIM($E106)," ",""))+1)</f>
         <v/>
@@ -4731,8 +4747,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D107" s="14" t="n"/>
-      <c r="E107" s="15" t="n"/>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>잠언 2장 6절</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>대저 여호와는 지혜를 주시며 지식과 명철을 그 입에서 내심이며</t>
+        </is>
+      </c>
       <c r="F107" s="16">
         <f>IF($E107="","",LEN(SUBSTITUTE($E107," ",""))+LEN(TRIM($E107))-LEN(SUBSTITUTE(TRIM($E107)," ",""))+1)</f>
         <v/>
@@ -4758,8 +4782,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D108" s="14" t="n"/>
-      <c r="E108" s="15" t="n"/>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>잠언 3장 3절</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>인자와 진리가 네게서 떠나지 말게 하고 그것을 네 목에 매며 네 마음판에 새기라</t>
+        </is>
+      </c>
       <c r="F108" s="16">
         <f>IF($E108="","",LEN(SUBSTITUTE($E108," ",""))+LEN(TRIM($E108))-LEN(SUBSTITUTE(TRIM($E108)," ",""))+1)</f>
         <v/>
@@ -4785,8 +4817,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D109" s="14" t="n"/>
-      <c r="E109" s="15" t="n"/>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>잠언 3장 5-6절</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>너는 마음을 다하여 여호와를 신뢰하고 네 명철을 의지하지 말라 너는 범사에 그를 인정하라 그리하면 네 길을 지도하시리라</t>
+        </is>
+      </c>
       <c r="F109" s="16">
         <f>IF($E109="","",LEN(SUBSTITUTE($E109," ",""))+LEN(TRIM($E109))-LEN(SUBSTITUTE(TRIM($E109)," ",""))+1)</f>
         <v/>
@@ -4812,8 +4852,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D110" s="14" t="n"/>
-      <c r="E110" s="15" t="n"/>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>잠언 3장 7절</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>스스로 지혜롭게 여기지 말지어다 여호와를 경외하며 악을 떠날지어다</t>
+        </is>
+      </c>
       <c r="F110" s="16">
         <f>IF($E110="","",LEN(SUBSTITUTE($E110," ",""))+LEN(TRIM($E110))-LEN(SUBSTITUTE(TRIM($E110)," ",""))+1)</f>
         <v/>
@@ -4839,8 +4887,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D111" s="14" t="n"/>
-      <c r="E111" s="15" t="n"/>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>잠언 3장 9절</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>네 재물과 네 소산물의 처음 익은 열매로 여호와를 공경하라</t>
+        </is>
+      </c>
       <c r="F111" s="16">
         <f>IF($E111="","",LEN(SUBSTITUTE($E111," ",""))+LEN(TRIM($E111))-LEN(SUBSTITUTE(TRIM($E111)," ",""))+1)</f>
         <v/>
@@ -4866,8 +4922,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D112" s="14" t="n"/>
-      <c r="E112" s="15" t="n"/>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>잠언 3장 11절</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>내 아들아 여호와의 징계를 경히 여기지 말라 그 꾸지람을 싫어하지 말라</t>
+        </is>
+      </c>
       <c r="F112" s="16">
         <f>IF($E112="","",LEN(SUBSTITUTE($E112," ",""))+LEN(TRIM($E112))-LEN(SUBSTITUTE(TRIM($E112)," ",""))+1)</f>
         <v/>
@@ -4893,8 +4957,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D113" s="14" t="n"/>
-      <c r="E113" s="15" t="n"/>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>잠언 3장 12절</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>대저 여호와께서 그 사랑하시는 자를 징계하시기를 마치 아비가 그 기뻐하는 아들을 징계함 같이 하시느니라</t>
+        </is>
+      </c>
       <c r="F113" s="16">
         <f>IF($E113="","",LEN(SUBSTITUTE($E113," ",""))+LEN(TRIM($E113))-LEN(SUBSTITUTE(TRIM($E113)," ",""))+1)</f>
         <v/>
@@ -4920,8 +4992,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D114" s="14" t="n"/>
-      <c r="E114" s="15" t="n"/>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>잠언 3장 27절</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>네 손이 선을 베풀 힘이 있거든 마땅히 받을 자에게 베풀기를 아끼지 말며</t>
+        </is>
+      </c>
       <c r="F114" s="16">
         <f>IF($E114="","",LEN(SUBSTITUTE($E114," ",""))+LEN(TRIM($E114))-LEN(SUBSTITUTE(TRIM($E114)," ",""))+1)</f>
         <v/>
@@ -4947,8 +5027,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D115" s="14" t="n"/>
-      <c r="E115" s="15" t="n"/>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>잠언 4장 7절</t>
+        </is>
+      </c>
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>지혜가 제일이니 지혜를 얻으라 네가 얻은 모든 것을 가지고 명철을 얻을지니라</t>
+        </is>
+      </c>
       <c r="F115" s="16">
         <f>IF($E115="","",LEN(SUBSTITUTE($E115," ",""))+LEN(TRIM($E115))-LEN(SUBSTITUTE(TRIM($E115)," ",""))+1)</f>
         <v/>
@@ -4974,8 +5062,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D116" s="14" t="n"/>
-      <c r="E116" s="15" t="n"/>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>잠언 4장 18절</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="inlineStr">
+        <is>
+          <t>의인의 길은 돋는 햇살 같아서 크게 빛나 한낮의 광명에 이르거니와</t>
+        </is>
+      </c>
       <c r="F116" s="16">
         <f>IF($E116="","",LEN(SUBSTITUTE($E116," ",""))+LEN(TRIM($E116))-LEN(SUBSTITUTE(TRIM($E116)," ",""))+1)</f>
         <v/>
@@ -5001,8 +5097,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D117" s="14" t="n"/>
-      <c r="E117" s="15" t="n"/>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>잠언 4장 23절</t>
+        </is>
+      </c>
+      <c r="E117" s="15" t="inlineStr">
+        <is>
+          <t>모든 지킬 만한 것 중에 더욱 네 마음을 지키라 생명의 근원이 이에서 남이니라</t>
+        </is>
+      </c>
       <c r="F117" s="16">
         <f>IF($E117="","",LEN(SUBSTITUTE($E117," ",""))+LEN(TRIM($E117))-LEN(SUBSTITUTE(TRIM($E117)," ",""))+1)</f>
         <v/>
@@ -5028,8 +5132,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D118" s="14" t="n"/>
-      <c r="E118" s="15" t="n"/>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>잠언 6장 6절</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>게으른 자여 개미에게 가서 그가 하는 것을 보고 지혜를 얻으라</t>
+        </is>
+      </c>
       <c r="F118" s="16">
         <f>IF($E118="","",LEN(SUBSTITUTE($E118," ",""))+LEN(TRIM($E118))-LEN(SUBSTITUTE(TRIM($E118)," ",""))+1)</f>
         <v/>
@@ -5055,8 +5167,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D119" s="14" t="n"/>
-      <c r="E119" s="15" t="n"/>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>잠언 8장 17절</t>
+        </is>
+      </c>
+      <c r="E119" s="15" t="inlineStr">
+        <is>
+          <t>나를 사랑하는 자들이 나의 사랑을 입으며 나를 간절히 찾는 자가 나를 만날 것이니라</t>
+        </is>
+      </c>
       <c r="F119" s="16">
         <f>IF($E119="","",LEN(SUBSTITUTE($E119," ",""))+LEN(TRIM($E119))-LEN(SUBSTITUTE(TRIM($E119)," ",""))+1)</f>
         <v/>
@@ -5082,8 +5202,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D120" s="14" t="n"/>
-      <c r="E120" s="15" t="n"/>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>잠언 9장 10절</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="inlineStr">
+        <is>
+          <t>여호와를 경외하는 것이 지혜의 근본이요 거룩하신 자를 아는 것이 명철이니라</t>
+        </is>
+      </c>
       <c r="F120" s="16">
         <f>IF($E120="","",LEN(SUBSTITUTE($E120," ",""))+LEN(TRIM($E120))-LEN(SUBSTITUTE(TRIM($E120)," ",""))+1)</f>
         <v/>
@@ -5109,8 +5237,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D121" s="14" t="n"/>
-      <c r="E121" s="15" t="n"/>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>잠언 10장 12절</t>
+        </is>
+      </c>
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>미움은 다툼을 일으켜도 사랑은 모든 허물을 가리느니라</t>
+        </is>
+      </c>
       <c r="F121" s="16">
         <f>IF($E121="","",LEN(SUBSTITUTE($E121," ",""))+LEN(TRIM($E121))-LEN(SUBSTITUTE(TRIM($E121)," ",""))+1)</f>
         <v/>
@@ -5136,8 +5272,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D122" s="14" t="n"/>
-      <c r="E122" s="15" t="n"/>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>잠언 10장 19절</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="inlineStr">
+        <is>
+          <t>말이 많으면 허물을 면하기 어려우나 그 입술을 제어하는 자는 지혜가 있느니라</t>
+        </is>
+      </c>
       <c r="F122" s="16">
         <f>IF($E122="","",LEN(SUBSTITUTE($E122," ",""))+LEN(TRIM($E122))-LEN(SUBSTITUTE(TRIM($E122)," ",""))+1)</f>
         <v/>
@@ -5163,8 +5307,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D123" s="14" t="n"/>
-      <c r="E123" s="15" t="n"/>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>잠언 10장 22절</t>
+        </is>
+      </c>
+      <c r="E123" s="15" t="inlineStr">
+        <is>
+          <t>여호와께서 주시는 복은 사람을 부하게 하고 근심을 겸하여 주지 아니하시느니라</t>
+        </is>
+      </c>
       <c r="F123" s="16">
         <f>IF($E123="","",LEN(SUBSTITUTE($E123," ",""))+LEN(TRIM($E123))-LEN(SUBSTITUTE(TRIM($E123)," ",""))+1)</f>
         <v/>
@@ -5190,8 +5342,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D124" s="14" t="n"/>
-      <c r="E124" s="15" t="n"/>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>잠언 11장 2절</t>
+        </is>
+      </c>
+      <c r="E124" s="15" t="inlineStr">
+        <is>
+          <t>교만이 오면 욕도 오거니와 겸손한 자에게는 지혜가 있느니라</t>
+        </is>
+      </c>
       <c r="F124" s="16">
         <f>IF($E124="","",LEN(SUBSTITUTE($E124," ",""))+LEN(TRIM($E124))-LEN(SUBSTITUTE(TRIM($E124)," ",""))+1)</f>
         <v/>
@@ -5217,8 +5377,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D125" s="14" t="n"/>
-      <c r="E125" s="15" t="n"/>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>잠언 11장 24절</t>
+        </is>
+      </c>
+      <c r="E125" s="15" t="inlineStr">
+        <is>
+          <t>흩어 구제하여도 더욱 부하게 되는 일이 있나니 과도히 아껴도 가난하게 될 뿐이니라</t>
+        </is>
+      </c>
       <c r="F125" s="16">
         <f>IF($E125="","",LEN(SUBSTITUTE($E125," ",""))+LEN(TRIM($E125))-LEN(SUBSTITUTE(TRIM($E125)," ",""))+1)</f>
         <v/>
@@ -5244,8 +5412,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D126" s="14" t="n"/>
-      <c r="E126" s="15" t="n"/>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>잠언 11장 25절</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="inlineStr">
+        <is>
+          <t>구제를 좋아하는 자는 풍족하여질 것이요 남을 윤택하게 하는 자는 자기도 윤택하여지리라</t>
+        </is>
+      </c>
       <c r="F126" s="16">
         <f>IF($E126="","",LEN(SUBSTITUTE($E126," ",""))+LEN(TRIM($E126))-LEN(SUBSTITUTE(TRIM($E126)," ",""))+1)</f>
         <v/>
@@ -5271,8 +5447,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D127" s="14" t="n"/>
-      <c r="E127" s="15" t="n"/>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>잠언 12장 15절</t>
+        </is>
+      </c>
+      <c r="E127" s="15" t="inlineStr">
+        <is>
+          <t>미련한 자는 자기 행위를 바른 줄로 여기나 지혜로운 자는 권고를 듣느니라</t>
+        </is>
+      </c>
       <c r="F127" s="16">
         <f>IF($E127="","",LEN(SUBSTITUTE($E127," ",""))+LEN(TRIM($E127))-LEN(SUBSTITUTE(TRIM($E127)," ",""))+1)</f>
         <v/>
@@ -5298,8 +5482,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D128" s="14" t="n"/>
-      <c r="E128" s="15" t="n"/>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>잠언 12장 25절</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="inlineStr">
+        <is>
+          <t>근심이 사람의 마음에 있으면 그것으로 번뇌하게 되나 선한 말은 그것을 즐겁게 하느니라</t>
+        </is>
+      </c>
       <c r="F128" s="16">
         <f>IF($E128="","",LEN(SUBSTITUTE($E128," ",""))+LEN(TRIM($E128))-LEN(SUBSTITUTE(TRIM($E128)," ",""))+1)</f>
         <v/>
@@ -5325,8 +5517,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D129" s="14" t="n"/>
-      <c r="E129" s="15" t="n"/>
+      <c r="D129" s="14" t="inlineStr">
+        <is>
+          <t>잠언 13장 3절</t>
+        </is>
+      </c>
+      <c r="E129" s="15" t="inlineStr">
+        <is>
+          <t>입을 지키는 자는 자기의 생명을 보전하나 입술을 크게 벌리는 자에게는 멸망이 오느니라</t>
+        </is>
+      </c>
       <c r="F129" s="16">
         <f>IF($E129="","",LEN(SUBSTITUTE($E129," ",""))+LEN(TRIM($E129))-LEN(SUBSTITUTE(TRIM($E129)," ",""))+1)</f>
         <v/>
@@ -5352,8 +5552,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D130" s="14" t="n"/>
-      <c r="E130" s="15" t="n"/>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>잠언 13장 20절</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="inlineStr">
+        <is>
+          <t>지혜로운 자와 동행하면 지혜를 얻고 미련한 자와 사귀면 해를 받느니라</t>
+        </is>
+      </c>
       <c r="F130" s="16">
         <f>IF($E130="","",LEN(SUBSTITUTE($E130," ",""))+LEN(TRIM($E130))-LEN(SUBSTITUTE(TRIM($E130)," ",""))+1)</f>
         <v/>
@@ -5379,8 +5587,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D131" s="14" t="n"/>
-      <c r="E131" s="15" t="n"/>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>잠언 14장 12절</t>
+        </is>
+      </c>
+      <c r="E131" s="15" t="inlineStr">
+        <is>
+          <t>어떤 길은 사람이 보기에 바르나 필경은 사망의 길이니라</t>
+        </is>
+      </c>
       <c r="F131" s="16">
         <f>IF($E131="","",LEN(SUBSTITUTE($E131," ",""))+LEN(TRIM($E131))-LEN(SUBSTITUTE(TRIM($E131)," ",""))+1)</f>
         <v/>
@@ -5406,8 +5622,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D132" s="14" t="n"/>
-      <c r="E132" s="15" t="n"/>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>잠언 14장 26절</t>
+        </is>
+      </c>
+      <c r="E132" s="15" t="inlineStr">
+        <is>
+          <t>여호와를 경외하는 자에게는 견고한 의뢰가 있나니 그 자녀들에게 피난처가 있으리라</t>
+        </is>
+      </c>
       <c r="F132" s="16">
         <f>IF($E132="","",LEN(SUBSTITUTE($E132," ",""))+LEN(TRIM($E132))-LEN(SUBSTITUTE(TRIM($E132)," ",""))+1)</f>
         <v/>
@@ -5433,8 +5657,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D133" s="14" t="n"/>
-      <c r="E133" s="15" t="n"/>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>잠언 14장 34절</t>
+        </is>
+      </c>
+      <c r="E133" s="15" t="inlineStr">
+        <is>
+          <t>공의는 나라를 영화롭게 하고 죄는 백성을 욕되게 하느니라</t>
+        </is>
+      </c>
       <c r="F133" s="16">
         <f>IF($E133="","",LEN(SUBSTITUTE($E133," ",""))+LEN(TRIM($E133))-LEN(SUBSTITUTE(TRIM($E133)," ",""))+1)</f>
         <v/>
@@ -5460,8 +5692,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D134" s="14" t="n"/>
-      <c r="E134" s="15" t="n"/>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>잠언 15장 1절</t>
+        </is>
+      </c>
+      <c r="E134" s="15" t="inlineStr">
+        <is>
+          <t>유순한 대답은 분노를 쉬게 하여도 과격한 말은 노를 격동하느니라</t>
+        </is>
+      </c>
       <c r="F134" s="16">
         <f>IF($E134="","",LEN(SUBSTITUTE($E134," ",""))+LEN(TRIM($E134))-LEN(SUBSTITUTE(TRIM($E134)," ",""))+1)</f>
         <v/>
@@ -5487,8 +5727,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D135" s="14" t="n"/>
-      <c r="E135" s="15" t="n"/>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>잠언 15장 3절</t>
+        </is>
+      </c>
+      <c r="E135" s="15" t="inlineStr">
+        <is>
+          <t>여호와의 눈은 어디서든지 악인과 선인을 감찰하시느니라</t>
+        </is>
+      </c>
       <c r="F135" s="16">
         <f>IF($E135="","",LEN(SUBSTITUTE($E135," ",""))+LEN(TRIM($E135))-LEN(SUBSTITUTE(TRIM($E135)," ",""))+1)</f>
         <v/>
@@ -5514,8 +5762,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D136" s="14" t="n"/>
-      <c r="E136" s="15" t="n"/>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>잠언 15장 13절</t>
+        </is>
+      </c>
+      <c r="E136" s="15" t="inlineStr">
+        <is>
+          <t>마음의 즐거움은 얼굴을 빛나게 하여도 마음의 근심은 심령을 상하게 하느니라</t>
+        </is>
+      </c>
       <c r="F136" s="16">
         <f>IF($E136="","",LEN(SUBSTITUTE($E136," ",""))+LEN(TRIM($E136))-LEN(SUBSTITUTE(TRIM($E136)," ",""))+1)</f>
         <v/>
@@ -5541,8 +5797,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D137" s="14" t="n"/>
-      <c r="E137" s="15" t="n"/>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>잠언 15장 16절</t>
+        </is>
+      </c>
+      <c r="E137" s="15" t="inlineStr">
+        <is>
+          <t>가산이 적어도 여호와를 경외하는 것이 크게 부하고 번뇌하는 것보다 나으니라</t>
+        </is>
+      </c>
       <c r="F137" s="16">
         <f>IF($E137="","",LEN(SUBSTITUTE($E137," ",""))+LEN(TRIM($E137))-LEN(SUBSTITUTE(TRIM($E137)," ",""))+1)</f>
         <v/>
@@ -5568,8 +5832,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D138" s="14" t="n"/>
-      <c r="E138" s="15" t="n"/>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>잠언 15장 17절</t>
+        </is>
+      </c>
+      <c r="E138" s="15" t="inlineStr">
+        <is>
+          <t>채소를 먹으며 서로 사랑하는 것이 살진 소를 먹으며 서로 미워하는 것보다 나으니라</t>
+        </is>
+      </c>
       <c r="F138" s="16">
         <f>IF($E138="","",LEN(SUBSTITUTE($E138," ",""))+LEN(TRIM($E138))-LEN(SUBSTITUTE(TRIM($E138)," ",""))+1)</f>
         <v/>
@@ -5595,8 +5867,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D139" s="14" t="n"/>
-      <c r="E139" s="15" t="n"/>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>잠언 16장 1절</t>
+        </is>
+      </c>
+      <c r="E139" s="15" t="inlineStr">
+        <is>
+          <t>마음의 경영은 사람에게 있어도 말의 응답은 여호와께로부터 나오느니라</t>
+        </is>
+      </c>
       <c r="F139" s="16">
         <f>IF($E139="","",LEN(SUBSTITUTE($E139," ",""))+LEN(TRIM($E139))-LEN(SUBSTITUTE(TRIM($E139)," ",""))+1)</f>
         <v/>
@@ -5622,8 +5902,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D140" s="14" t="n"/>
-      <c r="E140" s="15" t="n"/>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>잠언 16장 3절</t>
+        </is>
+      </c>
+      <c r="E140" s="15" t="inlineStr">
+        <is>
+          <t>너의 행사를 여호와께 맡기라 그리하면 네가 경영하는 것이 이루어지리라</t>
+        </is>
+      </c>
       <c r="F140" s="16">
         <f>IF($E140="","",LEN(SUBSTITUTE($E140," ",""))+LEN(TRIM($E140))-LEN(SUBSTITUTE(TRIM($E140)," ",""))+1)</f>
         <v/>
@@ -5649,8 +5937,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D141" s="14" t="n"/>
-      <c r="E141" s="15" t="n"/>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>잠언 16장 7절</t>
+        </is>
+      </c>
+      <c r="E141" s="15" t="inlineStr">
+        <is>
+          <t>사람의 행위가 여호와를 기쁘시게 하면 그 사람의 원수라도 그와 더불어 화목하게 하시느니라</t>
+        </is>
+      </c>
       <c r="F141" s="16">
         <f>IF($E141="","",LEN(SUBSTITUTE($E141," ",""))+LEN(TRIM($E141))-LEN(SUBSTITUTE(TRIM($E141)," ",""))+1)</f>
         <v/>
@@ -5676,8 +5972,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D142" s="14" t="n"/>
-      <c r="E142" s="15" t="n"/>
+      <c r="D142" s="14" t="inlineStr">
+        <is>
+          <t>잠언 16장 9절</t>
+        </is>
+      </c>
+      <c r="E142" s="15" t="inlineStr">
+        <is>
+          <t>사람이 마음으로 자기의 길을 계획할지라도 그의 걸음을 인도하시는 이는 여호와시니라</t>
+        </is>
+      </c>
       <c r="F142" s="16">
         <f>IF($E142="","",LEN(SUBSTITUTE($E142," ",""))+LEN(TRIM($E142))-LEN(SUBSTITUTE(TRIM($E142)," ",""))+1)</f>
         <v/>
@@ -5703,8 +6007,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D143" s="14" t="n"/>
-      <c r="E143" s="15" t="n"/>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>잠언 16장 18절</t>
+        </is>
+      </c>
+      <c r="E143" s="15" t="inlineStr">
+        <is>
+          <t>교만은 패망의 선봉이요 거만한 마음은 넘어짐의 앞잡이니라</t>
+        </is>
+      </c>
       <c r="F143" s="16">
         <f>IF($E143="","",LEN(SUBSTITUTE($E143," ",""))+LEN(TRIM($E143))-LEN(SUBSTITUTE(TRIM($E143)," ",""))+1)</f>
         <v/>
@@ -5730,8 +6042,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D144" s="14" t="n"/>
-      <c r="E144" s="15" t="n"/>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>잠언 16장 24절</t>
+        </is>
+      </c>
+      <c r="E144" s="15" t="inlineStr">
+        <is>
+          <t>선한 말은 꿀송이 같아서 마음에 달고 뼈에 양약이 되느니라</t>
+        </is>
+      </c>
       <c r="F144" s="16">
         <f>IF($E144="","",LEN(SUBSTITUTE($E144," ",""))+LEN(TRIM($E144))-LEN(SUBSTITUTE(TRIM($E144)," ",""))+1)</f>
         <v/>
@@ -5757,8 +6077,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D145" s="14" t="n"/>
-      <c r="E145" s="15" t="n"/>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>잠언 16장 32절</t>
+        </is>
+      </c>
+      <c r="E145" s="15" t="inlineStr">
+        <is>
+          <t>노하기를 더디하는 자는 용사보다 낫고 자기의 마음을 다스리는 자는 성을 빼앗는 자보다 나으니라</t>
+        </is>
+      </c>
       <c r="F145" s="16">
         <f>IF($E145="","",LEN(SUBSTITUTE($E145," ",""))+LEN(TRIM($E145))-LEN(SUBSTITUTE(TRIM($E145)," ",""))+1)</f>
         <v/>
@@ -5784,8 +6112,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D146" s="14" t="n"/>
-      <c r="E146" s="15" t="n"/>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>잠언 17장 1절</t>
+        </is>
+      </c>
+      <c r="E146" s="15" t="inlineStr">
+        <is>
+          <t>마른 떡 한 조각만 있고도 화목하는 것이 제육이 집에 가득하고도 다투는 것보다 나으니라</t>
+        </is>
+      </c>
       <c r="F146" s="16">
         <f>IF($E146="","",LEN(SUBSTITUTE($E146," ",""))+LEN(TRIM($E146))-LEN(SUBSTITUTE(TRIM($E146)," ",""))+1)</f>
         <v/>
@@ -5811,8 +6147,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D147" s="14" t="n"/>
-      <c r="E147" s="15" t="n"/>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>잠언 17장 3절</t>
+        </is>
+      </c>
+      <c r="E147" s="15" t="inlineStr">
+        <is>
+          <t>도가니는 은을, 풀무는 금을 연단하거니와 여호와는 마음을 연단하시느니라</t>
+        </is>
+      </c>
       <c r="F147" s="16">
         <f>IF($E147="","",LEN(SUBSTITUTE($E147," ",""))+LEN(TRIM($E147))-LEN(SUBSTITUTE(TRIM($E147)," ",""))+1)</f>
         <v/>
@@ -5838,8 +6182,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D148" s="14" t="n"/>
-      <c r="E148" s="15" t="n"/>
+      <c r="D148" s="14" t="inlineStr">
+        <is>
+          <t>잠언 17장 17절</t>
+        </is>
+      </c>
+      <c r="E148" s="15" t="inlineStr">
+        <is>
+          <t>친구는 사랑이 끊어지지 아니하고 형제는 위급한 때를 위하여 났느니라</t>
+        </is>
+      </c>
       <c r="F148" s="16">
         <f>IF($E148="","",LEN(SUBSTITUTE($E148," ",""))+LEN(TRIM($E148))-LEN(SUBSTITUTE(TRIM($E148)," ",""))+1)</f>
         <v/>
@@ -5865,8 +6217,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D149" s="14" t="n"/>
-      <c r="E149" s="15" t="n"/>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>잠언 17장 22절</t>
+        </is>
+      </c>
+      <c r="E149" s="15" t="inlineStr">
+        <is>
+          <t>마음의 즐거움은 양약이라도 심령의 근심은 뼈를 마르게 하느니라</t>
+        </is>
+      </c>
       <c r="F149" s="16">
         <f>IF($E149="","",LEN(SUBSTITUTE($E149," ",""))+LEN(TRIM($E149))-LEN(SUBSTITUTE(TRIM($E149)," ",""))+1)</f>
         <v/>
@@ -5892,8 +6252,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D150" s="14" t="n"/>
-      <c r="E150" s="15" t="n"/>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>잠언 18장 10절</t>
+        </is>
+      </c>
+      <c r="E150" s="15" t="inlineStr">
+        <is>
+          <t>여호와의 이름은 견고한 망대라 의인은 그리로 달려가서 안전함을 얻느니라</t>
+        </is>
+      </c>
       <c r="F150" s="16">
         <f>IF($E150="","",LEN(SUBSTITUTE($E150," ",""))+LEN(TRIM($E150))-LEN(SUBSTITUTE(TRIM($E150)," ",""))+1)</f>
         <v/>
@@ -5919,8 +6287,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D151" s="14" t="n"/>
-      <c r="E151" s="15" t="n"/>
+      <c r="D151" s="14" t="inlineStr">
+        <is>
+          <t>잠언 18장 21절</t>
+        </is>
+      </c>
+      <c r="E151" s="15" t="inlineStr">
+        <is>
+          <t>죽고 사는 것이 혀의 힘에 달렸나니 혀를 쓰기 좋아하는 자는 혀의 열매를 먹으리라</t>
+        </is>
+      </c>
       <c r="F151" s="16">
         <f>IF($E151="","",LEN(SUBSTITUTE($E151," ",""))+LEN(TRIM($E151))-LEN(SUBSTITUTE(TRIM($E151)," ",""))+1)</f>
         <v/>
@@ -5946,8 +6322,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D152" s="14" t="n"/>
-      <c r="E152" s="15" t="n"/>
+      <c r="D152" s="14" t="inlineStr">
+        <is>
+          <t>잠언 19장 11절</t>
+        </is>
+      </c>
+      <c r="E152" s="15" t="inlineStr">
+        <is>
+          <t>노하기를 더디 하는 것이 사람의 슬기요 허물을 용서하는 것이 자기의 영광이니라</t>
+        </is>
+      </c>
       <c r="F152" s="16">
         <f>IF($E152="","",LEN(SUBSTITUTE($E152," ",""))+LEN(TRIM($E152))-LEN(SUBSTITUTE(TRIM($E152)," ",""))+1)</f>
         <v/>
@@ -5973,8 +6357,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D153" s="14" t="n"/>
-      <c r="E153" s="15" t="n"/>
+      <c r="D153" s="14" t="inlineStr">
+        <is>
+          <t>잠언 19장 17절</t>
+        </is>
+      </c>
+      <c r="E153" s="15" t="inlineStr">
+        <is>
+          <t>가난한 자를 불쌍히 여기는 것은 여호와께 꾸어 드리는 것이니 그의 선행을 그에게 갚아 주시리라</t>
+        </is>
+      </c>
       <c r="F153" s="16">
         <f>IF($E153="","",LEN(SUBSTITUTE($E153," ",""))+LEN(TRIM($E153))-LEN(SUBSTITUTE(TRIM($E153)," ",""))+1)</f>
         <v/>
@@ -6000,8 +6392,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D154" s="14" t="n"/>
-      <c r="E154" s="15" t="n"/>
+      <c r="D154" s="14" t="inlineStr">
+        <is>
+          <t>잠언 19장 21절</t>
+        </is>
+      </c>
+      <c r="E154" s="15" t="inlineStr">
+        <is>
+          <t>사람의 마음에는 많은 계획이 있어도 오직 여호와의 뜻만이 완전히 서리라</t>
+        </is>
+      </c>
       <c r="F154" s="16">
         <f>IF($E154="","",LEN(SUBSTITUTE($E154," ",""))+LEN(TRIM($E154))-LEN(SUBSTITUTE(TRIM($E154)," ",""))+1)</f>
         <v/>
@@ -6027,8 +6427,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D155" s="14" t="n"/>
-      <c r="E155" s="15" t="n"/>
+      <c r="D155" s="14" t="inlineStr">
+        <is>
+          <t>잠언 21장 3절</t>
+        </is>
+      </c>
+      <c r="E155" s="15" t="inlineStr">
+        <is>
+          <t>공의와 정의를 행하는 것은 제사 드리는 것보다 여호와께서 기쁘게 여기시느니라</t>
+        </is>
+      </c>
       <c r="F155" s="16">
         <f>IF($E155="","",LEN(SUBSTITUTE($E155," ",""))+LEN(TRIM($E155))-LEN(SUBSTITUTE(TRIM($E155)," ",""))+1)</f>
         <v/>
@@ -6054,8 +6462,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D156" s="14" t="n"/>
-      <c r="E156" s="15" t="n"/>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>잠언 21장 31절</t>
+        </is>
+      </c>
+      <c r="E156" s="15" t="inlineStr">
+        <is>
+          <t>싸울 날을 위하여 마병을 예비하거니와 이김은 여호와께 있느니라</t>
+        </is>
+      </c>
       <c r="F156" s="16">
         <f>IF($E156="","",LEN(SUBSTITUTE($E156," ",""))+LEN(TRIM($E156))-LEN(SUBSTITUTE(TRIM($E156)," ",""))+1)</f>
         <v/>
@@ -6081,8 +6497,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D157" s="14" t="n"/>
-      <c r="E157" s="15" t="n"/>
+      <c r="D157" s="14" t="inlineStr">
+        <is>
+          <t>잠언 22장 1절</t>
+        </is>
+      </c>
+      <c r="E157" s="15" t="inlineStr">
+        <is>
+          <t>많은 재물보다 명예를 택할 것이요 은이나 금보다 은총을 더욱 택할 것이니라</t>
+        </is>
+      </c>
       <c r="F157" s="16">
         <f>IF($E157="","",LEN(SUBSTITUTE($E157," ",""))+LEN(TRIM($E157))-LEN(SUBSTITUTE(TRIM($E157)," ",""))+1)</f>
         <v/>
@@ -6108,8 +6532,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D158" s="14" t="n"/>
-      <c r="E158" s="15" t="n"/>
+      <c r="D158" s="14" t="inlineStr">
+        <is>
+          <t>잠언 22장 4절</t>
+        </is>
+      </c>
+      <c r="E158" s="15" t="inlineStr">
+        <is>
+          <t>겸손과 여호와를 경외함의 보상은 재물과 영광과 생명이니라</t>
+        </is>
+      </c>
       <c r="F158" s="16">
         <f>IF($E158="","",LEN(SUBSTITUTE($E158," ",""))+LEN(TRIM($E158))-LEN(SUBSTITUTE(TRIM($E158)," ",""))+1)</f>
         <v/>
@@ -6135,8 +6567,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D159" s="14" t="n"/>
-      <c r="E159" s="15" t="n"/>
+      <c r="D159" s="14" t="inlineStr">
+        <is>
+          <t>잠언 22장 6절</t>
+        </is>
+      </c>
+      <c r="E159" s="15" t="inlineStr">
+        <is>
+          <t>마땅히 행할 길을 아이에게 가르치라 그리하면 늙어도 그것을 떠나지 아니하리라</t>
+        </is>
+      </c>
       <c r="F159" s="16">
         <f>IF($E159="","",LEN(SUBSTITUTE($E159," ",""))+LEN(TRIM($E159))-LEN(SUBSTITUTE(TRIM($E159)," ",""))+1)</f>
         <v/>
@@ -6162,8 +6602,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D160" s="14" t="n"/>
-      <c r="E160" s="15" t="n"/>
+      <c r="D160" s="14" t="inlineStr">
+        <is>
+          <t>잠언 24장 16절</t>
+        </is>
+      </c>
+      <c r="E160" s="15" t="inlineStr">
+        <is>
+          <t>대저 의인은 일곱 번 넘어질지라도 다시 일어나려니와 악인은 재앙으로 말미암아 엎드러지느니라</t>
+        </is>
+      </c>
       <c r="F160" s="16">
         <f>IF($E160="","",LEN(SUBSTITUTE($E160," ",""))+LEN(TRIM($E160))-LEN(SUBSTITUTE(TRIM($E160)," ",""))+1)</f>
         <v/>
@@ -6189,8 +6637,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D161" s="14" t="n"/>
-      <c r="E161" s="15" t="n"/>
+      <c r="D161" s="14" t="inlineStr">
+        <is>
+          <t>잠언 25장 11절</t>
+        </is>
+      </c>
+      <c r="E161" s="15" t="inlineStr">
+        <is>
+          <t>경우에 합당한 말은 아로새긴 은 쟁반에 금 사과니라</t>
+        </is>
+      </c>
       <c r="F161" s="16">
         <f>IF($E161="","",LEN(SUBSTITUTE($E161," ",""))+LEN(TRIM($E161))-LEN(SUBSTITUTE(TRIM($E161)," ",""))+1)</f>
         <v/>
@@ -6216,8 +6672,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D162" s="14" t="n"/>
-      <c r="E162" s="15" t="n"/>
+      <c r="D162" s="14" t="inlineStr">
+        <is>
+          <t>잠언 27장 1절</t>
+        </is>
+      </c>
+      <c r="E162" s="15" t="inlineStr">
+        <is>
+          <t>너는 내일 일을 자랑하지 말라 하루 동안에 무슨 일이 일어날는지 네가 알 수 없음이니라</t>
+        </is>
+      </c>
       <c r="F162" s="16">
         <f>IF($E162="","",LEN(SUBSTITUTE($E162," ",""))+LEN(TRIM($E162))-LEN(SUBSTITUTE(TRIM($E162)," ",""))+1)</f>
         <v/>
@@ -6243,8 +6707,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D163" s="14" t="n"/>
-      <c r="E163" s="15" t="n"/>
+      <c r="D163" s="14" t="inlineStr">
+        <is>
+          <t>잠언 27장 2절</t>
+        </is>
+      </c>
+      <c r="E163" s="15" t="inlineStr">
+        <is>
+          <t>타인이 너를 칭찬하게 하고 네 입으로는 하지 말며 외인이 너를 칭찬하게 하고 네 입술로는 하지 말지니라</t>
+        </is>
+      </c>
       <c r="F163" s="16">
         <f>IF($E163="","",LEN(SUBSTITUTE($E163," ",""))+LEN(TRIM($E163))-LEN(SUBSTITUTE(TRIM($E163)," ",""))+1)</f>
         <v/>
@@ -6270,8 +6742,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D164" s="14" t="n"/>
-      <c r="E164" s="15" t="n"/>
+      <c r="D164" s="14" t="inlineStr">
+        <is>
+          <t>잠언 27장 17절</t>
+        </is>
+      </c>
+      <c r="E164" s="15" t="inlineStr">
+        <is>
+          <t>철이 철을 날카롭게 하는 것 같이 사람이 그의 친구의 얼굴을 빛나게 하느니라</t>
+        </is>
+      </c>
       <c r="F164" s="16">
         <f>IF($E164="","",LEN(SUBSTITUTE($E164," ",""))+LEN(TRIM($E164))-LEN(SUBSTITUTE(TRIM($E164)," ",""))+1)</f>
         <v/>
@@ -6297,8 +6777,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D165" s="14" t="n"/>
-      <c r="E165" s="15" t="n"/>
+      <c r="D165" s="14" t="inlineStr">
+        <is>
+          <t>잠언 28장 1절</t>
+        </is>
+      </c>
+      <c r="E165" s="15" t="inlineStr">
+        <is>
+          <t>악인은 쫓아오는 자가 없어도 도망하나 의인은 사자 같이 담대하니라</t>
+        </is>
+      </c>
       <c r="F165" s="16">
         <f>IF($E165="","",LEN(SUBSTITUTE($E165," ",""))+LEN(TRIM($E165))-LEN(SUBSTITUTE(TRIM($E165)," ",""))+1)</f>
         <v/>
@@ -6324,8 +6812,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D166" s="14" t="n"/>
-      <c r="E166" s="15" t="n"/>
+      <c r="D166" s="14" t="inlineStr">
+        <is>
+          <t>잠언 28장 13절</t>
+        </is>
+      </c>
+      <c r="E166" s="15" t="inlineStr">
+        <is>
+          <t>자기의 죄를 숨기는 자는 형통하지 못하나 죄를 자복하고 버리는 자는 불쌍히 여김을 받으리라</t>
+        </is>
+      </c>
       <c r="F166" s="16">
         <f>IF($E166="","",LEN(SUBSTITUTE($E166," ",""))+LEN(TRIM($E166))-LEN(SUBSTITUTE(TRIM($E166)," ",""))+1)</f>
         <v/>
@@ -6351,8 +6847,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D167" s="14" t="n"/>
-      <c r="E167" s="15" t="n"/>
+      <c r="D167" s="14" t="inlineStr">
+        <is>
+          <t>잠언 29장 18절</t>
+        </is>
+      </c>
+      <c r="E167" s="15" t="inlineStr">
+        <is>
+          <t>묵시가 없으면 백성이 방자히 행하거니와 율법을 지키는 자는 복이 있느니라</t>
+        </is>
+      </c>
       <c r="F167" s="16">
         <f>IF($E167="","",LEN(SUBSTITUTE($E167," ",""))+LEN(TRIM($E167))-LEN(SUBSTITUTE(TRIM($E167)," ",""))+1)</f>
         <v/>
@@ -6378,8 +6882,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D168" s="14" t="n"/>
-      <c r="E168" s="15" t="n"/>
+      <c r="D168" s="14" t="inlineStr">
+        <is>
+          <t>잠언 29장 25절</t>
+        </is>
+      </c>
+      <c r="E168" s="15" t="inlineStr">
+        <is>
+          <t>사람을 두려워하면 올무에 걸리게 되거니와 여호와를 의지하는 자는 안전하리라</t>
+        </is>
+      </c>
       <c r="F168" s="16">
         <f>IF($E168="","",LEN(SUBSTITUTE($E168," ",""))+LEN(TRIM($E168))-LEN(SUBSTITUTE(TRIM($E168)," ",""))+1)</f>
         <v/>
@@ -6405,8 +6917,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D169" s="14" t="n"/>
-      <c r="E169" s="15" t="n"/>
+      <c r="D169" s="14" t="inlineStr">
+        <is>
+          <t>잠언 30장 5절</t>
+        </is>
+      </c>
+      <c r="E169" s="15" t="inlineStr">
+        <is>
+          <t>하나님의 말씀은 다 순전하며 하나님은 그를 의지하는 자의 방패시니라</t>
+        </is>
+      </c>
       <c r="F169" s="16">
         <f>IF($E169="","",LEN(SUBSTITUTE($E169," ",""))+LEN(TRIM($E169))-LEN(SUBSTITUTE(TRIM($E169)," ",""))+1)</f>
         <v/>
@@ -6432,8 +6952,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D170" s="14" t="n"/>
-      <c r="E170" s="15" t="n"/>
+      <c r="D170" s="14" t="inlineStr">
+        <is>
+          <t>잠언 31장 10절</t>
+        </is>
+      </c>
+      <c r="E170" s="15" t="inlineStr">
+        <is>
+          <t>누가 현숙한 여인을 찾아 얻겠느냐 그의 값은 진주보다 더 하니라</t>
+        </is>
+      </c>
       <c r="F170" s="16">
         <f>IF($E170="","",LEN(SUBSTITUTE($E170," ",""))+LEN(TRIM($E170))-LEN(SUBSTITUTE(TRIM($E170)," ",""))+1)</f>
         <v/>
@@ -6459,8 +6987,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D171" s="14" t="n"/>
-      <c r="E171" s="15" t="n"/>
+      <c r="D171" s="14" t="inlineStr">
+        <is>
+          <t>잠언 31장 30절</t>
+        </is>
+      </c>
+      <c r="E171" s="15" t="inlineStr">
+        <is>
+          <t>고운 것도 거짓되고 아름다운 것도 헛되나 오직 여호와를 경외하는 여자는 칭찬을 받을 것이라</t>
+        </is>
+      </c>
       <c r="F171" s="16">
         <f>IF($E171="","",LEN(SUBSTITUTE($E171," ",""))+LEN(TRIM($E171))-LEN(SUBSTITUTE(TRIM($E171)," ",""))+1)</f>
         <v/>
@@ -6486,8 +7022,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D172" s="14" t="n"/>
-      <c r="E172" s="15" t="n"/>
+      <c r="D172" s="14" t="inlineStr">
+        <is>
+          <t>전도서 3장 1절</t>
+        </is>
+      </c>
+      <c r="E172" s="15" t="inlineStr">
+        <is>
+          <t>범사에 기한이 있고 천하 만사가 다 때가 있나니</t>
+        </is>
+      </c>
       <c r="F172" s="16">
         <f>IF($E172="","",LEN(SUBSTITUTE($E172," ",""))+LEN(TRIM($E172))-LEN(SUBSTITUTE(TRIM($E172)," ",""))+1)</f>
         <v/>
@@ -6513,8 +7057,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D173" s="14" t="n"/>
-      <c r="E173" s="15" t="n"/>
+      <c r="D173" s="14" t="inlineStr">
+        <is>
+          <t>전도서 4장 6절</t>
+        </is>
+      </c>
+      <c r="E173" s="15" t="inlineStr">
+        <is>
+          <t>두 손에 가득하고 수고하며 바람을 잡는 것보다 한 손에만 가득하고 평온함이 더 나으니라</t>
+        </is>
+      </c>
       <c r="F173" s="16">
         <f>IF($E173="","",LEN(SUBSTITUTE($E173," ",""))+LEN(TRIM($E173))-LEN(SUBSTITUTE(TRIM($E173)," ",""))+1)</f>
         <v/>
@@ -6540,8 +7092,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D174" s="14" t="n"/>
-      <c r="E174" s="15" t="n"/>
+      <c r="D174" s="14" t="inlineStr">
+        <is>
+          <t>전도서 4장 9절</t>
+        </is>
+      </c>
+      <c r="E174" s="15" t="inlineStr">
+        <is>
+          <t>두 사람이 한 사람보다 나음은 그들이 수고함으로 좋은 상을 얻을 것임이라</t>
+        </is>
+      </c>
       <c r="F174" s="16">
         <f>IF($E174="","",LEN(SUBSTITUTE($E174," ",""))+LEN(TRIM($E174))-LEN(SUBSTITUTE(TRIM($E174)," ",""))+1)</f>
         <v/>
@@ -6567,8 +7127,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D175" s="14" t="n"/>
-      <c r="E175" s="15" t="n"/>
+      <c r="D175" s="14" t="inlineStr">
+        <is>
+          <t>전도서 4장 12절</t>
+        </is>
+      </c>
+      <c r="E175" s="15" t="inlineStr">
+        <is>
+          <t>한 사람이면 패하겠거니와 두 사람이면 맞설 수 있나니 세 겹 줄은 쉽게 끊어지지 아니하느니라</t>
+        </is>
+      </c>
       <c r="F175" s="16">
         <f>IF($E175="","",LEN(SUBSTITUTE($E175," ",""))+LEN(TRIM($E175))-LEN(SUBSTITUTE(TRIM($E175)," ",""))+1)</f>
         <v/>
@@ -6594,8 +7162,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D176" s="14" t="n"/>
-      <c r="E176" s="15" t="n"/>
+      <c r="D176" s="14" t="inlineStr">
+        <is>
+          <t>전도서 5장 10절</t>
+        </is>
+      </c>
+      <c r="E176" s="15" t="inlineStr">
+        <is>
+          <t>은을 사랑하는 자는 은으로 만족하지 못하고 풍요를 사랑하는 자는 소득으로 만족하지 아니하나니 이것도 헛되도다</t>
+        </is>
+      </c>
       <c r="F176" s="16">
         <f>IF($E176="","",LEN(SUBSTITUTE($E176," ",""))+LEN(TRIM($E176))-LEN(SUBSTITUTE(TRIM($E176)," ",""))+1)</f>
         <v/>
@@ -6621,8 +7197,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="D177" s="14" t="n"/>
-      <c r="E177" s="15" t="n"/>
+      <c r="D177" s="14" t="inlineStr">
+        <is>
+          <t>전도서 7장 1절</t>
+        </is>
+      </c>
+      <c r="E177" s="15" t="inlineStr">
+        <is>
+          <t>좋은 이름이 좋은 기름보다 낫고 죽는 날이 출생하는 날보다 나으며</t>
+        </is>
+      </c>
       <c r="F177" s="16">
         <f>IF($E177="","",LEN(SUBSTITUTE($E177," ",""))+LEN(TRIM($E177))-LEN(SUBSTITUTE(TRIM($E177)," ",""))+1)</f>
         <v/>
@@ -6648,8 +7232,16 @@
           <t>일</t>
         </is>
       </c>
-      <c r="D178" s="14" t="n"/>
-      <c r="E178" s="15" t="n"/>
+      <c r="D178" s="14" t="inlineStr">
+        <is>
+          <t>전도서 7장 8절</t>
+        </is>
+      </c>
+      <c r="E178" s="15" t="inlineStr">
+        <is>
+          <t>일의 끝이 시작보다 낫고 참는 마음이 교만한 마음보다 나으니</t>
+        </is>
+      </c>
       <c r="F178" s="16">
         <f>IF($E178="","",LEN(SUBSTITUTE($E178," ",""))+LEN(TRIM($E178))-LEN(SUBSTITUTE(TRIM($E178)," ",""))+1)</f>
         <v/>
@@ -6675,8 +7267,16 @@
           <t>월</t>
         </is>
       </c>
-      <c r="D179" s="14" t="n"/>
-      <c r="E179" s="15" t="n"/>
+      <c r="D179" s="14" t="inlineStr">
+        <is>
+          <t>전도서 9장 10절</t>
+        </is>
+      </c>
+      <c r="E179" s="15" t="inlineStr">
+        <is>
+          <t>네 손이 일을 얻는 대로 힘을 다하여 할지어다 네가 장차 들어갈 스올에는 일도 없고 계획도 없고 지식도 없고 지혜도 없음이니라</t>
+        </is>
+      </c>
       <c r="F179" s="16">
         <f>IF($E179="","",LEN(SUBSTITUTE($E179," ",""))+LEN(TRIM($E179))-LEN(SUBSTITUTE(TRIM($E179)," ",""))+1)</f>
         <v/>
@@ -6702,8 +7302,16 @@
           <t>화</t>
         </is>
       </c>
-      <c r="D180" s="14" t="n"/>
-      <c r="E180" s="15" t="n"/>
+      <c r="D180" s="14" t="inlineStr">
+        <is>
+          <t>전도서 11장 1절</t>
+        </is>
+      </c>
+      <c r="E180" s="15" t="inlineStr">
+        <is>
+          <t>너는 네 떡을 물 위에 던져라 여러 날 후에 도로 찾으리라</t>
+        </is>
+      </c>
       <c r="F180" s="16">
         <f>IF($E180="","",LEN(SUBSTITUTE($E180," ",""))+LEN(TRIM($E180))-LEN(SUBSTITUTE(TRIM($E180)," ",""))+1)</f>
         <v/>
@@ -6729,8 +7337,16 @@
           <t>수</t>
         </is>
       </c>
-      <c r="D181" s="14" t="n"/>
-      <c r="E181" s="15" t="n"/>
+      <c r="D181" s="14" t="inlineStr">
+        <is>
+          <t>전도서 12장 1절</t>
+        </is>
+      </c>
+      <c r="E181" s="15" t="inlineStr">
+        <is>
+          <t>너는 청년의 때에 너의 창조주를 기억하라 곧 곤고한 날이 이르기 전에, 나는 아무 낙이 없다고 할 해들이 가깝기 전에</t>
+        </is>
+      </c>
       <c r="F181" s="16">
         <f>IF($E181="","",LEN(SUBSTITUTE($E181," ",""))+LEN(TRIM($E181))-LEN(SUBSTITUTE(TRIM($E181)," ",""))+1)</f>
         <v/>
@@ -6756,8 +7372,16 @@
           <t>목</t>
         </is>
       </c>
-      <c r="D182" s="14" t="n"/>
-      <c r="E182" s="15" t="n"/>
+      <c r="D182" s="14" t="inlineStr">
+        <is>
+          <t>전도서 12장 13절</t>
+        </is>
+      </c>
+      <c r="E182" s="15" t="inlineStr">
+        <is>
+          <t>일의 결국을 다 들었으니 하나님을 경외하고 그의 명령들을 지킬지어다 이것이 모든 사람의 본분이니라</t>
+        </is>
+      </c>
       <c r="F182" s="16">
         <f>IF($E182="","",LEN(SUBSTITUTE($E182," ",""))+LEN(TRIM($E182))-LEN(SUBSTITUTE(TRIM($E182)," ",""))+1)</f>
         <v/>
@@ -6783,8 +7407,16 @@
           <t>금</t>
         </is>
       </c>
-      <c r="D183" s="14" t="n"/>
-      <c r="E183" s="15" t="n"/>
+      <c r="D183" s="14" t="inlineStr">
+        <is>
+          <t>전도서 12장 14절</t>
+        </is>
+      </c>
+      <c r="E183" s="15" t="inlineStr">
+        <is>
+          <t>하나님은 모든 행위와 모든 은밀한 일을 선악 간에 심판하시리라</t>
+        </is>
+      </c>
       <c r="F183" s="16">
         <f>IF($E183="","",LEN(SUBSTITUTE($E183," ",""))+LEN(TRIM($E183))-LEN(SUBSTITUTE(TRIM($E183)," ",""))+1)</f>
         <v/>

--- a/psalm/시편말씀액자_구절입력_180.xlsx
+++ b/psalm/시편말씀액자_구절입력_180.xlsx
@@ -723,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="3" customWidth="1" style="24" min="1" max="1"/>
@@ -733,6 +733,7 @@
     <col width="30" customWidth="1" style="24" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="34.05" customHeight="1" s="24">
       <c r="B2" s="28" t="inlineStr">
         <is>
@@ -743,10 +744,11 @@
     <row r="3">
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>2026년 09월 21일(월) 1일차 시작 · 하루에 한 편씩 180일</t>
-        </is>
-      </c>
-    </row>
+          <t>2026년 09월 12일(토) 1일차 시작 · 하루에 한 편씩 180일</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5" ht="19.5" customHeight="1" s="24">
       <c r="B5" s="27" t="inlineStr">
         <is>
@@ -768,6 +770,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="19.5" customHeight="1" s="24">
       <c r="B9" s="27" t="inlineStr">
         <is>
@@ -789,6 +792,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="19.5" customHeight="1" s="24">
       <c r="B13" s="27" t="inlineStr">
         <is>
@@ -803,6 +807,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="1" t="inlineStr">
         <is>
@@ -965,6 +970,8 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24" ht="19.5" customHeight="1" s="24">
       <c r="B24" s="27" t="inlineStr">
         <is>
@@ -986,6 +993,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="19.5" customHeight="1" s="24">
       <c r="B28" s="27" t="inlineStr">
         <is>
@@ -1000,6 +1008,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="19.5" customHeight="1" s="24">
       <c r="B31" s="30" t="inlineStr">
         <is>
@@ -1010,10 +1019,11 @@
     <row r="32" ht="32" customHeight="1" s="24">
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>9월 17일(목)까지 주시면 9월 21일(월) 시작에 맞출 수 있습니다. 다 못 채우셔도 괜찮습니다 — 앞에서부터 30편만 있어도 한 달을 갑니다.</t>
-        </is>
-      </c>
-    </row>
+          <t>180편을 모두 채웠습니다(2026-09-11). 2026년 9월 12일(토) 1일차부터 하루에 한 편씩 열립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34" ht="30" customHeight="1" s="24">
       <c r="B34" s="29" t="inlineStr">
         <is>
@@ -1073,6 +1083,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="26" customHeight="1" s="24">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1126,12 +1137,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
@@ -1161,12 +1172,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
@@ -1196,12 +1207,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -1231,12 +1242,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -1266,12 +1277,12 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -1301,12 +1312,12 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -1340,12 +1351,12 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -1375,12 +1386,12 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -1410,12 +1421,12 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -1449,12 +1460,12 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -1484,12 +1495,12 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -1519,12 +1530,12 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -1554,12 +1565,12 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -1589,12 +1600,12 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -1624,12 +1635,12 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -1659,12 +1670,12 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
@@ -1694,12 +1705,12 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -1729,12 +1740,12 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -1764,12 +1775,12 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -1799,12 +1810,12 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -1834,12 +1845,12 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
@@ -1869,12 +1880,12 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
@@ -1904,12 +1915,12 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -1939,12 +1950,12 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
@@ -1974,12 +1985,12 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -2009,12 +2020,12 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
@@ -2044,12 +2055,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -2079,12 +2090,12 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -2114,12 +2125,12 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -2149,12 +2160,12 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -2184,12 +2195,12 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -2219,12 +2230,12 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -2254,12 +2265,12 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -2289,12 +2300,12 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -2324,12 +2335,12 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -2359,12 +2370,12 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -2394,12 +2405,12 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -2429,12 +2440,12 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
@@ -2464,12 +2475,12 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
@@ -2499,12 +2510,12 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
@@ -2534,12 +2545,12 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
@@ -2569,12 +2580,12 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -2604,12 +2615,12 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
@@ -2639,12 +2650,12 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
@@ -2674,12 +2685,12 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
@@ -2709,12 +2720,12 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
@@ -2744,12 +2755,12 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
@@ -2779,12 +2790,12 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
@@ -2814,12 +2825,12 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C52" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
@@ -2849,12 +2860,12 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
@@ -2884,12 +2895,12 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
@@ -2919,12 +2930,12 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
@@ -2954,12 +2965,12 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
@@ -2989,12 +3000,12 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -3024,12 +3035,12 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
@@ -3059,12 +3070,12 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -3094,12 +3105,12 @@
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
@@ -3129,12 +3140,12 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
@@ -3164,12 +3175,12 @@
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
@@ -3199,12 +3210,12 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D63" s="14" t="inlineStr">
@@ -3234,12 +3245,12 @@
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
@@ -3269,12 +3280,12 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D65" s="14" t="inlineStr">
@@ -3304,12 +3315,12 @@
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C66" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
@@ -3339,12 +3350,12 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
@@ -3374,12 +3385,12 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
@@ -3409,12 +3420,12 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
@@ -3444,12 +3455,12 @@
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
@@ -3479,12 +3490,12 @@
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
@@ -3514,12 +3525,12 @@
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
@@ -3549,12 +3560,12 @@
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
@@ -3584,12 +3595,12 @@
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
@@ -3619,12 +3630,12 @@
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
@@ -3654,12 +3665,12 @@
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
@@ -3689,12 +3700,12 @@
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
@@ -3724,12 +3735,12 @@
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
@@ -3759,12 +3770,12 @@
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
@@ -3794,12 +3805,12 @@
       </c>
       <c r="B80" s="18" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="C80" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
@@ -3829,12 +3840,12 @@
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
@@ -3864,12 +3875,12 @@
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
@@ -3899,12 +3910,12 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
@@ -3934,12 +3945,12 @@
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
@@ -3969,12 +3980,12 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
@@ -4004,12 +4015,12 @@
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
@@ -4039,12 +4050,12 @@
       </c>
       <c r="B87" s="18" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
@@ -4074,12 +4085,12 @@
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
@@ -4109,12 +4120,12 @@
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
@@ -4144,12 +4155,12 @@
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
@@ -4179,12 +4190,12 @@
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
@@ -4214,12 +4225,12 @@
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -4249,12 +4260,12 @@
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
@@ -4284,12 +4295,12 @@
       </c>
       <c r="B94" s="18" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="C94" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
@@ -4319,12 +4330,12 @@
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
@@ -4354,12 +4365,12 @@
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
@@ -4389,12 +4400,12 @@
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
@@ -4424,12 +4435,12 @@
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
@@ -4459,12 +4470,12 @@
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
@@ -4494,12 +4505,12 @@
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
@@ -4529,12 +4540,12 @@
       </c>
       <c r="B101" s="18" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="C101" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
@@ -4564,12 +4575,12 @@
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
@@ -4599,12 +4610,12 @@
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D103" s="14" t="inlineStr">
@@ -4634,12 +4645,12 @@
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
@@ -4669,12 +4680,12 @@
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D105" s="14" t="inlineStr">
@@ -4704,12 +4715,12 @@
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
@@ -4739,12 +4750,12 @@
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
@@ -4774,12 +4785,12 @@
       </c>
       <c r="B108" s="18" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="C108" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
@@ -4809,12 +4820,12 @@
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
@@ -4844,12 +4855,12 @@
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
@@ -4879,12 +4890,12 @@
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
@@ -4914,12 +4925,12 @@
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
@@ -4949,12 +4960,12 @@
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="C113" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
@@ -4984,12 +4995,12 @@
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
@@ -5019,12 +5030,12 @@
       </c>
       <c r="B115" s="18" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="C115" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
@@ -5054,12 +5065,12 @@
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
@@ -5089,12 +5100,12 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
@@ -5124,12 +5135,12 @@
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
@@ -5159,12 +5170,12 @@
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
@@ -5194,12 +5205,12 @@
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
@@ -5229,12 +5240,12 @@
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
@@ -5264,12 +5275,12 @@
       </c>
       <c r="B122" s="18" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="C122" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
@@ -5299,12 +5310,12 @@
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
@@ -5334,12 +5345,12 @@
       </c>
       <c r="B124" s="13" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="C124" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
@@ -5369,12 +5380,12 @@
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="C125" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
@@ -5404,12 +5415,12 @@
       </c>
       <c r="B126" s="13" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="C126" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
@@ -5439,12 +5450,12 @@
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="C127" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
@@ -5474,12 +5485,12 @@
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
@@ -5509,12 +5520,12 @@
       </c>
       <c r="B129" s="18" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="C129" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
@@ -5544,12 +5555,12 @@
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
@@ -5579,12 +5590,12 @@
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D131" s="14" t="inlineStr">
@@ -5614,12 +5625,12 @@
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
@@ -5649,12 +5660,12 @@
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D133" s="14" t="inlineStr">
@@ -5684,12 +5695,12 @@
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
@@ -5719,12 +5730,12 @@
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="C135" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D135" s="14" t="inlineStr">
@@ -5754,12 +5765,12 @@
       </c>
       <c r="B136" s="18" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="C136" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
@@ -5789,12 +5800,12 @@
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="C137" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D137" s="14" t="inlineStr">
@@ -5824,12 +5835,12 @@
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
@@ -5859,12 +5870,12 @@
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="C139" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D139" s="14" t="inlineStr">
@@ -5894,12 +5905,12 @@
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
@@ -5929,12 +5940,12 @@
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="C141" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D141" s="14" t="inlineStr">
@@ -5964,12 +5975,12 @@
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
@@ -5999,12 +6010,12 @@
       </c>
       <c r="B143" s="18" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="C143" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D143" s="14" t="inlineStr">
@@ -6034,12 +6045,12 @@
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
@@ -6069,12 +6080,12 @@
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D145" s="14" t="inlineStr">
@@ -6104,12 +6115,12 @@
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
@@ -6139,12 +6150,12 @@
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="C147" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D147" s="14" t="inlineStr">
@@ -6174,12 +6185,12 @@
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
@@ -6209,12 +6220,12 @@
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="C149" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D149" s="14" t="inlineStr">
@@ -6244,12 +6255,12 @@
       </c>
       <c r="B150" s="18" t="inlineStr">
         <is>
-          <t>2027-02-14</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="C150" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
@@ -6279,12 +6290,12 @@
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="C151" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D151" s="14" t="inlineStr">
@@ -6314,12 +6325,12 @@
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>2027-02-16</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="C152" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D152" s="14" t="inlineStr">
@@ -6349,12 +6360,12 @@
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="C153" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D153" s="14" t="inlineStr">
@@ -6384,12 +6395,12 @@
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>2027-02-18</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D154" s="14" t="inlineStr">
@@ -6419,12 +6430,12 @@
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="C155" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D155" s="14" t="inlineStr">
@@ -6454,12 +6465,12 @@
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D156" s="14" t="inlineStr">
@@ -6489,12 +6500,12 @@
       </c>
       <c r="B157" s="18" t="inlineStr">
         <is>
-          <t>2027-02-21</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="C157" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D157" s="14" t="inlineStr">
@@ -6524,12 +6535,12 @@
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D158" s="14" t="inlineStr">
@@ -6559,12 +6570,12 @@
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="C159" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D159" s="14" t="inlineStr">
@@ -6594,12 +6605,12 @@
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D160" s="14" t="inlineStr">
@@ -6629,12 +6640,12 @@
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="C161" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D161" s="14" t="inlineStr">
@@ -6664,12 +6675,12 @@
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D162" s="14" t="inlineStr">
@@ -6699,12 +6710,12 @@
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="C163" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D163" s="14" t="inlineStr">
@@ -6734,12 +6745,12 @@
       </c>
       <c r="B164" s="18" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="C164" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D164" s="14" t="inlineStr">
@@ -6769,12 +6780,12 @@
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="C165" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D165" s="14" t="inlineStr">
@@ -6804,12 +6815,12 @@
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D166" s="14" t="inlineStr">
@@ -6839,12 +6850,12 @@
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="C167" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D167" s="14" t="inlineStr">
@@ -6874,12 +6885,12 @@
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>2027-03-04</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D168" s="14" t="inlineStr">
@@ -6909,12 +6920,12 @@
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="C169" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D169" s="14" t="inlineStr">
@@ -6944,12 +6955,12 @@
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D170" s="14" t="inlineStr">
@@ -6979,12 +6990,12 @@
       </c>
       <c r="B171" s="18" t="inlineStr">
         <is>
-          <t>2027-03-07</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="C171" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D171" s="14" t="inlineStr">
@@ -7014,12 +7025,12 @@
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>2027-03-08</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="C172" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D172" s="14" t="inlineStr">
@@ -7049,12 +7060,12 @@
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>2027-03-09</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="C173" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D173" s="14" t="inlineStr">
@@ -7084,12 +7095,12 @@
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>2027-03-10</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D174" s="14" t="inlineStr">
@@ -7119,12 +7130,12 @@
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>2027-03-11</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="C175" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D175" s="14" t="inlineStr">
@@ -7154,12 +7165,12 @@
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>2027-03-12</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D176" s="14" t="inlineStr">
@@ -7189,12 +7200,12 @@
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
-          <t>2027-03-13</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="C177" s="13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="D177" s="14" t="inlineStr">
@@ -7224,12 +7235,12 @@
       </c>
       <c r="B178" s="18" t="inlineStr">
         <is>
-          <t>2027-03-14</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="C178" s="19" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="D178" s="14" t="inlineStr">
@@ -7259,12 +7270,12 @@
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>2027-03-15</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="C179" s="13" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>토</t>
         </is>
       </c>
       <c r="D179" s="14" t="inlineStr">
@@ -7294,12 +7305,12 @@
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>2027-03-16</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
       <c r="D180" s="14" t="inlineStr">
@@ -7329,12 +7340,12 @@
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>2027-03-17</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="C181" s="13" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="D181" s="14" t="inlineStr">
@@ -7364,12 +7375,12 @@
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>2027-03-18</t>
+          <t>2027-03-09</t>
         </is>
       </c>
       <c r="C182" s="13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="D182" s="14" t="inlineStr">
@@ -7399,12 +7410,12 @@
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
-          <t>2027-03-19</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="C183" s="13" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="D183" s="14" t="inlineStr">
@@ -7460,7 +7471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="26" customWidth="1" style="24" min="2" max="2"/>
@@ -7468,6 +7479,7 @@
     <col width="44" customWidth="1" style="24" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="24">
       <c r="B2" s="32" t="inlineStr">
         <is>
@@ -7475,6 +7487,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1" s="24">
       <c r="B4" s="20" t="inlineStr">
         <is>
@@ -7571,6 +7584,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="32" customHeight="1" s="24">
       <c r="B11" s="29" t="inlineStr">
         <is>
